--- a/2026/Q1/Books information for unlatching upload_ku_2026-01.xlsx
+++ b/2026/Q1/Books information for unlatching upload_ku_2026-01.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="88">
   <si>
     <t xml:space="preserve">Type of Document (Book or Chapter)</t>
   </si>
@@ -175,9 +175,6 @@
     <t xml:space="preserve">Kašćelan, Draško; Parafita Couto María del Carmen; Webb-Davies, Peredur; Pérez-Tattam, Rocío; Stadthagen-González, Hans </t>
   </si>
   <si>
-    <t xml:space="preserve">LAN009001</t>
-  </si>
-  <si>
     <t xml:space="preserve">10.5281/zenodo.18740570</t>
   </si>
   <si>
@@ -191,19 +188,13 @@
     <t xml:space="preserve">https://langsci-press.org/catalog/book/522</t>
   </si>
   <si>
-    <t xml:space="preserve">Language Science Press 2027</t>
-  </si>
-  <si>
     <t xml:space="preserve">The Austronesian languages of eastern Indonesia and Timor-Lest</t>
   </si>
   <si>
     <t xml:space="preserve"> Unravelling their prehistory and classification</t>
   </si>
   <si>
-    <t xml:space="preserve">Grimes, Charles E. ; Edwards, Owen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAN009002</t>
+    <t xml:space="preserve">Grimes, Charles E.; Edwards, Owen</t>
   </si>
   <si>
     <t xml:space="preserve">10.5281/zenodo.18323007</t>
@@ -224,16 +215,10 @@
     <t xml:space="preserve">https://langsci-press.org/catalog/book/526</t>
   </si>
   <si>
-    <t xml:space="preserve">Language Science Press 2028</t>
-  </si>
-  <si>
     <t xml:space="preserve">Modalidade e modo em português europeu</t>
   </si>
   <si>
     <t xml:space="preserve">Marques, Rui</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAN009003</t>
   </si>
   <si>
     <t xml:space="preserve">10.5281/zenodo.17788744</t>
@@ -253,9 +238,6 @@
     <t xml:space="preserve">https://langsci-press.org/catalog/book/554</t>
   </si>
   <si>
-    <t xml:space="preserve">Language Science Press 2029</t>
-  </si>
-  <si>
     <t xml:space="preserve">I always migrated by reindeer</t>
   </si>
   <si>
@@ -263,9 +245,6 @@
   </si>
   <si>
     <t xml:space="preserve">Pakendorf, Brigitte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAN009004</t>
   </si>
   <si>
     <t xml:space="preserve">10.5281/zenodo.18682200</t>
@@ -285,9 +264,6 @@
     <t xml:space="preserve">https://langsci-press.org/catalog/book/562</t>
   </si>
   <si>
-    <t xml:space="preserve">Language Science Press 2030</t>
-  </si>
-  <si>
     <t xml:space="preserve">Das Framing von Extremismusvarianten im medialen Diskurs der Jahre 1999–2021</t>
   </si>
   <si>
@@ -295,9 +271,6 @@
   </si>
   <si>
     <t xml:space="preserve">Feldmüller, Tim </t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAN009005</t>
   </si>
   <si>
     <t xml:space="preserve">10.5281/zenodo.18274343</t>
@@ -322,9 +295,6 @@
     <t xml:space="preserve">https://langsci-press.org/catalog/book/567</t>
   </si>
   <si>
-    <t xml:space="preserve">Language Science Press 2031</t>
-  </si>
-  <si>
     <t xml:space="preserve">Life and death on Karas</t>
   </si>
   <si>
@@ -332,9 +302,6 @@
   </si>
   <si>
     <t xml:space="preserve">Visser, Eline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAN009006</t>
   </si>
   <si>
     <t xml:space="preserve">10.5281/zenodo.19091196</t>
@@ -346,9 +313,6 @@
   </si>
   <si>
     <t xml:space="preserve">https://langsci-press.org/catalog/book/586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Language Science Press 2032</t>
   </si>
 </sst>
 </file>
@@ -514,7 +478,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -581,6 +545,10 @@
     </xf>
     <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1078,13 +1046,13 @@
       <c r="U2" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="V2" s="0" t="n">
+      <c r="V2" s="17" t="n">
         <v>298</v>
       </c>
       <c r="W2" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="X2" s="17"/>
+      <c r="X2" s="18"/>
       <c r="Y2" s="10" t="s">
         <v>44</v>
       </c>
@@ -1111,14 +1079,14 @@
       </c>
       <c r="G3" s="12"/>
       <c r="H3" s="9" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="I3" s="9"/>
       <c r="J3" s="9" t="s">
         <v>38</v>
       </c>
       <c r="K3" s="9" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="L3" s="12"/>
       <c r="M3" s="10" t="n">
@@ -1126,38 +1094,38 @@
       </c>
       <c r="N3" s="13"/>
       <c r="O3" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P3" s="12"/>
       <c r="Q3" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R3" s="15" t="n">
         <v>6</v>
       </c>
       <c r="S3" s="12"/>
       <c r="T3" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="U3" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="V3" s="0" t="n">
+      <c r="V3" s="17" t="n">
         <v>300</v>
       </c>
       <c r="W3" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="X3" s="17"/>
+      <c r="X3" s="18"/>
       <c r="Y3" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="AA3" s="17"/>
+        <v>52</v>
+      </c>
+      <c r="AA3" s="18"/>
       <c r="AB3" s="9" t="s">
         <v>45</v>
       </c>
       <c r="AG3" s="1" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1165,26 +1133,26 @@
         <v>33</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D4" s="12"/>
       <c r="E4" s="10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F4" s="9"/>
       <c r="G4" s="12"/>
       <c r="H4" s="9" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="I4" s="9"/>
       <c r="J4" s="9" t="s">
         <v>38</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="L4" s="12"/>
       <c r="M4" s="10" t="n">
@@ -1192,38 +1160,38 @@
       </c>
       <c r="N4" s="13"/>
       <c r="O4" s="14" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="P4" s="12"/>
       <c r="Q4" s="15" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="R4" s="15" t="n">
         <v>1</v>
       </c>
       <c r="S4" s="12"/>
-      <c r="T4" s="18" t="s">
-        <v>61</v>
+      <c r="T4" s="19" t="s">
+        <v>58</v>
       </c>
       <c r="U4" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="V4" s="0" t="n">
+      <c r="V4" s="17" t="n">
         <v>948</v>
       </c>
       <c r="W4" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="X4" s="17"/>
+      <c r="X4" s="18"/>
       <c r="Y4" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="AA4" s="17"/>
+        <v>59</v>
+      </c>
+      <c r="AA4" s="18"/>
       <c r="AB4" s="9" t="s">
         <v>45</v>
       </c>
       <c r="AG4" s="1" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1231,24 +1199,24 @@
         <v>33</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="12"/>
       <c r="E5" s="10" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F5" s="9"/>
       <c r="G5" s="12"/>
       <c r="H5" s="9" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="I5" s="9"/>
       <c r="J5" s="9" t="s">
         <v>38</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="L5" s="12"/>
       <c r="M5" s="10" t="n">
@@ -1256,38 +1224,38 @@
       </c>
       <c r="N5" s="13"/>
       <c r="O5" s="14" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="P5" s="12"/>
       <c r="Q5" s="15" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="R5" s="15" t="n">
         <v>15</v>
       </c>
       <c r="S5" s="12"/>
       <c r="T5" s="16" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="U5" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="V5" s="0" t="n">
+        <v>65</v>
+      </c>
+      <c r="V5" s="17" t="n">
         <v>204</v>
       </c>
       <c r="W5" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="X5" s="17"/>
+      <c r="X5" s="18"/>
       <c r="Y5" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="AA5" s="17"/>
+        <v>66</v>
+      </c>
+      <c r="AA5" s="18"/>
       <c r="AB5" s="9" t="s">
         <v>45</v>
       </c>
       <c r="AG5" s="1" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1295,26 +1263,26 @@
         <v>33</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="10" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F6" s="9"/>
       <c r="G6" s="12"/>
       <c r="H6" s="9" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="I6" s="9"/>
       <c r="J6" s="9" t="s">
         <v>38</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>2030</v>
+        <v>2026</v>
       </c>
       <c r="L6" s="12"/>
       <c r="M6" s="10" t="n">
@@ -1322,38 +1290,38 @@
       </c>
       <c r="N6" s="13"/>
       <c r="O6" s="14" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="P6" s="12"/>
       <c r="Q6" s="15" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="R6" s="15" t="n">
         <v>8</v>
       </c>
       <c r="S6" s="12"/>
       <c r="T6" s="16" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="U6" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="V6" s="0" t="n">
+      <c r="V6" s="17" t="n">
         <v>456</v>
       </c>
       <c r="W6" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="X6" s="17"/>
+      <c r="X6" s="18"/>
       <c r="Y6" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA6" s="17"/>
+        <v>73</v>
+      </c>
+      <c r="AA6" s="18"/>
       <c r="AB6" s="9" t="s">
         <v>45</v>
       </c>
       <c r="AG6" s="1" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1361,26 +1329,26 @@
         <v>33</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D7" s="12"/>
       <c r="E7" s="10" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="F7" s="9"/>
       <c r="G7" s="12"/>
       <c r="H7" s="9" t="s">
-        <v>85</v>
+        <v>37</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="9" t="s">
         <v>38</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>2031</v>
+        <v>2026</v>
       </c>
       <c r="L7" s="12"/>
       <c r="M7" s="10" t="n">
@@ -1388,38 +1356,38 @@
       </c>
       <c r="N7" s="13"/>
       <c r="O7" s="14" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="P7" s="12"/>
       <c r="Q7" s="15" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="R7" s="15" t="n">
         <v>2</v>
       </c>
       <c r="S7" s="12"/>
       <c r="T7" s="16" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="U7" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="V7" s="0" t="n">
+        <v>80</v>
+      </c>
+      <c r="V7" s="17" t="n">
         <v>328</v>
       </c>
       <c r="W7" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="X7" s="17"/>
+      <c r="X7" s="18"/>
       <c r="Y7" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="AA7" s="17"/>
+        <v>81</v>
+      </c>
+      <c r="AA7" s="18"/>
       <c r="AB7" s="9" t="s">
         <v>45</v>
       </c>
       <c r="AG7" s="1" t="s">
-        <v>91</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1427,57 +1395,57 @@
         <v>33</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>95</v>
+        <v>37</v>
       </c>
       <c r="J8" s="9" t="s">
         <v>38</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>2032</v>
+        <v>2026</v>
       </c>
       <c r="L8" s="12"/>
       <c r="M8" s="10" t="n">
         <v>9783961105670</v>
       </c>
-      <c r="N8" s="19"/>
+      <c r="N8" s="20"/>
       <c r="O8" s="14" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="Q8" s="15" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="R8" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="T8" s="20" t="s">
-        <v>97</v>
+      <c r="T8" s="21" t="s">
+        <v>86</v>
       </c>
       <c r="U8" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="V8" s="0" t="n">
+      <c r="V8" s="17" t="n">
         <v>308</v>
       </c>
       <c r="W8" s="10" t="s">
         <v>43</v>
       </c>
       <c r="Y8" s="10" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="AB8" s="9" t="s">
         <v>45</v>
       </c>
       <c r="AG8" s="1" t="s">
-        <v>99</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1485,2890 +1453,2890 @@
       <c r="C9" s="9"/>
       <c r="J9" s="9"/>
       <c r="L9" s="12"/>
-      <c r="N9" s="19"/>
+      <c r="N9" s="20"/>
     </row>
     <row r="10" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9"/>
       <c r="C10" s="9"/>
       <c r="J10" s="9"/>
       <c r="L10" s="12"/>
-      <c r="N10" s="19"/>
+      <c r="N10" s="20"/>
     </row>
     <row r="11" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9"/>
       <c r="J11" s="9"/>
       <c r="L11" s="12"/>
-      <c r="N11" s="19"/>
+      <c r="N11" s="20"/>
     </row>
     <row r="12" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="9"/>
       <c r="J12" s="9"/>
       <c r="L12" s="12"/>
-      <c r="N12" s="19"/>
+      <c r="N12" s="20"/>
     </row>
     <row r="13" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9"/>
       <c r="J13" s="9"/>
       <c r="L13" s="12"/>
-      <c r="N13" s="19"/>
+      <c r="N13" s="20"/>
     </row>
     <row r="14" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="9"/>
       <c r="J14" s="9"/>
       <c r="L14" s="12"/>
-      <c r="N14" s="19"/>
+      <c r="N14" s="20"/>
     </row>
     <row r="15" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9"/>
       <c r="J15" s="9"/>
       <c r="L15" s="12"/>
-      <c r="N15" s="19"/>
+      <c r="N15" s="20"/>
     </row>
     <row r="16" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="9"/>
       <c r="J16" s="9"/>
       <c r="L16" s="12"/>
-      <c r="N16" s="19"/>
+      <c r="N16" s="20"/>
     </row>
     <row r="17" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="9"/>
       <c r="J17" s="9"/>
       <c r="L17" s="12"/>
-      <c r="N17" s="19"/>
+      <c r="N17" s="20"/>
     </row>
     <row r="18" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="9"/>
       <c r="J18" s="9"/>
       <c r="L18" s="12"/>
-      <c r="N18" s="19"/>
+      <c r="N18" s="20"/>
     </row>
     <row r="19" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="9"/>
       <c r="J19" s="9"/>
       <c r="L19" s="12"/>
-      <c r="N19" s="19"/>
+      <c r="N19" s="20"/>
     </row>
     <row r="20" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="9"/>
       <c r="J20" s="9"/>
       <c r="L20" s="12"/>
-      <c r="N20" s="19"/>
+      <c r="N20" s="20"/>
     </row>
     <row r="21" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="9"/>
       <c r="J21" s="9"/>
       <c r="L21" s="12"/>
-      <c r="N21" s="19"/>
+      <c r="N21" s="20"/>
     </row>
     <row r="22" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="9"/>
       <c r="J22" s="9"/>
       <c r="L22" s="12"/>
-      <c r="N22" s="19"/>
+      <c r="N22" s="20"/>
       <c r="U22" s="9"/>
     </row>
     <row r="23" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="9"/>
       <c r="J23" s="9"/>
       <c r="L23" s="12"/>
-      <c r="N23" s="19"/>
+      <c r="N23" s="20"/>
     </row>
     <row r="24" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="9"/>
       <c r="J24" s="9"/>
       <c r="L24" s="12"/>
-      <c r="N24" s="19"/>
+      <c r="N24" s="20"/>
     </row>
     <row r="25" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="9"/>
       <c r="J25" s="9"/>
       <c r="L25" s="12"/>
-      <c r="N25" s="19"/>
+      <c r="N25" s="20"/>
       <c r="U25" s="9"/>
     </row>
     <row r="26" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="9"/>
       <c r="J26" s="9"/>
       <c r="L26" s="12"/>
-      <c r="N26" s="19"/>
+      <c r="N26" s="20"/>
     </row>
     <row r="27" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="9"/>
       <c r="J27" s="9"/>
       <c r="L27" s="12"/>
-      <c r="N27" s="19"/>
+      <c r="N27" s="20"/>
     </row>
     <row r="28" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="9"/>
       <c r="J28" s="9"/>
       <c r="L28" s="12"/>
-      <c r="N28" s="19"/>
+      <c r="N28" s="20"/>
     </row>
     <row r="29" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="9"/>
       <c r="J29" s="9"/>
       <c r="L29" s="12"/>
-      <c r="N29" s="19"/>
+      <c r="N29" s="20"/>
     </row>
     <row r="30" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="9"/>
       <c r="J30" s="9"/>
       <c r="L30" s="12"/>
-      <c r="N30" s="19"/>
+      <c r="N30" s="20"/>
     </row>
     <row r="31" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="9"/>
       <c r="J31" s="9"/>
       <c r="L31" s="12"/>
-      <c r="N31" s="19"/>
+      <c r="N31" s="20"/>
     </row>
     <row r="32" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="9"/>
       <c r="J32" s="9"/>
       <c r="L32" s="12"/>
-      <c r="N32" s="19"/>
+      <c r="N32" s="20"/>
     </row>
     <row r="33" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="9"/>
       <c r="J33" s="9"/>
       <c r="L33" s="12"/>
-      <c r="N33" s="19"/>
+      <c r="N33" s="20"/>
     </row>
     <row r="34" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="9"/>
       <c r="J34" s="9"/>
       <c r="L34" s="12"/>
-      <c r="N34" s="19"/>
+      <c r="N34" s="20"/>
     </row>
     <row r="35" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="9"/>
       <c r="J35" s="9"/>
       <c r="L35" s="12"/>
-      <c r="N35" s="19"/>
+      <c r="N35" s="20"/>
     </row>
     <row r="36" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="9"/>
       <c r="J36" s="9"/>
       <c r="L36" s="12"/>
-      <c r="N36" s="19"/>
+      <c r="N36" s="20"/>
     </row>
     <row r="37" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="9"/>
       <c r="J37" s="9"/>
       <c r="L37" s="12"/>
-      <c r="N37" s="19"/>
+      <c r="N37" s="20"/>
     </row>
     <row r="38" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="9"/>
       <c r="J38" s="9"/>
       <c r="L38" s="12"/>
-      <c r="N38" s="19"/>
+      <c r="N38" s="20"/>
     </row>
     <row r="39" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="9"/>
       <c r="J39" s="9"/>
       <c r="L39" s="12"/>
-      <c r="N39" s="19"/>
+      <c r="N39" s="20"/>
     </row>
     <row r="40" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="9"/>
       <c r="J40" s="9"/>
       <c r="L40" s="12"/>
-      <c r="N40" s="19"/>
+      <c r="N40" s="20"/>
     </row>
     <row r="41" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="9"/>
       <c r="J41" s="9"/>
       <c r="L41" s="12"/>
-      <c r="N41" s="19"/>
+      <c r="N41" s="20"/>
     </row>
     <row r="42" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="9"/>
       <c r="J42" s="9"/>
       <c r="L42" s="12"/>
-      <c r="N42" s="19"/>
+      <c r="N42" s="20"/>
     </row>
     <row r="43" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="9"/>
       <c r="J43" s="9"/>
       <c r="L43" s="12"/>
-      <c r="N43" s="19"/>
+      <c r="N43" s="20"/>
     </row>
     <row r="44" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="9"/>
       <c r="J44" s="9"/>
       <c r="L44" s="12"/>
-      <c r="N44" s="19"/>
+      <c r="N44" s="20"/>
     </row>
     <row r="45" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="9"/>
       <c r="J45" s="9"/>
       <c r="L45" s="12"/>
-      <c r="N45" s="19"/>
+      <c r="N45" s="20"/>
     </row>
     <row r="46" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="9"/>
       <c r="J46" s="9"/>
       <c r="L46" s="12"/>
-      <c r="N46" s="19"/>
+      <c r="N46" s="20"/>
     </row>
     <row r="47" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="9"/>
       <c r="J47" s="9"/>
       <c r="L47" s="12"/>
-      <c r="N47" s="19"/>
+      <c r="N47" s="20"/>
     </row>
     <row r="48" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="9"/>
       <c r="J48" s="9"/>
       <c r="L48" s="12"/>
-      <c r="N48" s="19"/>
+      <c r="N48" s="20"/>
     </row>
     <row r="49" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="9"/>
       <c r="J49" s="9"/>
       <c r="L49" s="12"/>
-      <c r="N49" s="19"/>
+      <c r="N49" s="20"/>
     </row>
     <row r="50" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="9"/>
       <c r="J50" s="9"/>
       <c r="L50" s="12"/>
-      <c r="N50" s="19"/>
+      <c r="N50" s="20"/>
     </row>
     <row r="51" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="9"/>
       <c r="J51" s="9"/>
       <c r="L51" s="12"/>
-      <c r="N51" s="19"/>
+      <c r="N51" s="20"/>
     </row>
     <row r="52" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="9"/>
       <c r="J52" s="9"/>
       <c r="L52" s="12"/>
-      <c r="N52" s="19"/>
+      <c r="N52" s="20"/>
     </row>
     <row r="53" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="9"/>
       <c r="J53" s="9"/>
       <c r="L53" s="12"/>
-      <c r="N53" s="19"/>
+      <c r="N53" s="20"/>
     </row>
     <row r="54" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="9"/>
       <c r="J54" s="9"/>
       <c r="L54" s="12"/>
-      <c r="N54" s="19"/>
+      <c r="N54" s="20"/>
     </row>
     <row r="55" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="9"/>
       <c r="J55" s="9"/>
       <c r="L55" s="12"/>
-      <c r="N55" s="19"/>
+      <c r="N55" s="20"/>
     </row>
     <row r="56" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="9"/>
       <c r="J56" s="9"/>
       <c r="L56" s="12"/>
-      <c r="N56" s="19"/>
+      <c r="N56" s="20"/>
     </row>
     <row r="57" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="9"/>
       <c r="J57" s="9"/>
       <c r="L57" s="12"/>
-      <c r="N57" s="19"/>
+      <c r="N57" s="20"/>
     </row>
     <row r="58" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="9"/>
       <c r="J58" s="9"/>
       <c r="L58" s="12"/>
-      <c r="N58" s="19"/>
+      <c r="N58" s="20"/>
     </row>
     <row r="59" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="9"/>
       <c r="J59" s="9"/>
       <c r="L59" s="12"/>
-      <c r="N59" s="19"/>
+      <c r="N59" s="20"/>
     </row>
     <row r="60" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="9"/>
       <c r="J60" s="9"/>
       <c r="L60" s="12"/>
-      <c r="N60" s="19"/>
+      <c r="N60" s="20"/>
     </row>
     <row r="61" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="9"/>
       <c r="J61" s="9"/>
       <c r="L61" s="12"/>
-      <c r="N61" s="19"/>
+      <c r="N61" s="20"/>
     </row>
     <row r="62" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="9"/>
       <c r="J62" s="9"/>
       <c r="L62" s="12"/>
-      <c r="N62" s="19"/>
+      <c r="N62" s="20"/>
     </row>
     <row r="63" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="9"/>
       <c r="J63" s="9"/>
       <c r="L63" s="12"/>
-      <c r="N63" s="19"/>
+      <c r="N63" s="20"/>
     </row>
     <row r="64" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="9"/>
       <c r="J64" s="9"/>
       <c r="L64" s="12"/>
-      <c r="N64" s="19"/>
+      <c r="N64" s="20"/>
     </row>
     <row r="65" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="9"/>
       <c r="J65" s="9"/>
       <c r="L65" s="12"/>
-      <c r="N65" s="19"/>
+      <c r="N65" s="20"/>
     </row>
     <row r="66" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="9"/>
       <c r="J66" s="9"/>
       <c r="L66" s="12"/>
-      <c r="N66" s="19"/>
+      <c r="N66" s="20"/>
     </row>
     <row r="67" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="9"/>
       <c r="J67" s="9"/>
       <c r="L67" s="12"/>
-      <c r="N67" s="19"/>
+      <c r="N67" s="20"/>
     </row>
     <row r="68" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="9"/>
       <c r="J68" s="9"/>
       <c r="L68" s="12"/>
-      <c r="N68" s="19"/>
+      <c r="N68" s="20"/>
     </row>
     <row r="69" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="9"/>
       <c r="J69" s="9"/>
       <c r="L69" s="12"/>
-      <c r="N69" s="19"/>
+      <c r="N69" s="20"/>
     </row>
     <row r="70" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="9"/>
       <c r="J70" s="9"/>
       <c r="L70" s="12"/>
-      <c r="N70" s="19"/>
+      <c r="N70" s="20"/>
     </row>
     <row r="71" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="9"/>
       <c r="J71" s="9"/>
       <c r="L71" s="12"/>
-      <c r="N71" s="19"/>
+      <c r="N71" s="20"/>
     </row>
     <row r="72" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="9"/>
       <c r="J72" s="9"/>
       <c r="L72" s="12"/>
-      <c r="N72" s="19"/>
+      <c r="N72" s="20"/>
     </row>
     <row r="73" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="9"/>
       <c r="J73" s="9"/>
       <c r="L73" s="12"/>
-      <c r="N73" s="19"/>
+      <c r="N73" s="20"/>
     </row>
     <row r="74" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="9"/>
       <c r="J74" s="9"/>
       <c r="L74" s="12"/>
-      <c r="N74" s="19"/>
+      <c r="N74" s="20"/>
     </row>
     <row r="75" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="9"/>
       <c r="J75" s="9"/>
       <c r="L75" s="12"/>
-      <c r="N75" s="19"/>
+      <c r="N75" s="20"/>
     </row>
     <row r="76" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="9"/>
       <c r="J76" s="9"/>
       <c r="L76" s="12"/>
-      <c r="N76" s="19"/>
+      <c r="N76" s="20"/>
     </row>
     <row r="77" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="9"/>
       <c r="J77" s="9"/>
       <c r="L77" s="12"/>
-      <c r="N77" s="19"/>
+      <c r="N77" s="20"/>
     </row>
     <row r="78" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="9"/>
       <c r="J78" s="9"/>
       <c r="L78" s="12"/>
-      <c r="N78" s="19"/>
+      <c r="N78" s="20"/>
     </row>
     <row r="79" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="9"/>
       <c r="J79" s="9"/>
       <c r="L79" s="12"/>
-      <c r="N79" s="19"/>
+      <c r="N79" s="20"/>
     </row>
     <row r="80" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="9"/>
       <c r="J80" s="9"/>
       <c r="L80" s="12"/>
-      <c r="N80" s="19"/>
+      <c r="N80" s="20"/>
     </row>
     <row r="81" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="9"/>
       <c r="J81" s="9"/>
       <c r="L81" s="12"/>
-      <c r="N81" s="19"/>
+      <c r="N81" s="20"/>
     </row>
     <row r="82" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="9"/>
       <c r="J82" s="9"/>
       <c r="L82" s="12"/>
-      <c r="N82" s="19"/>
+      <c r="N82" s="20"/>
     </row>
     <row r="83" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="9"/>
       <c r="J83" s="9"/>
       <c r="L83" s="12"/>
-      <c r="N83" s="19"/>
+      <c r="N83" s="20"/>
     </row>
     <row r="84" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="9"/>
       <c r="J84" s="9"/>
       <c r="L84" s="12"/>
-      <c r="N84" s="19"/>
+      <c r="N84" s="20"/>
     </row>
     <row r="85" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="9"/>
       <c r="J85" s="9"/>
       <c r="L85" s="12"/>
-      <c r="N85" s="19"/>
+      <c r="N85" s="20"/>
     </row>
     <row r="86" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="9"/>
       <c r="J86" s="9"/>
       <c r="L86" s="12"/>
-      <c r="N86" s="19"/>
+      <c r="N86" s="20"/>
     </row>
     <row r="87" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="9"/>
       <c r="J87" s="9"/>
       <c r="L87" s="12"/>
-      <c r="N87" s="19"/>
+      <c r="N87" s="20"/>
     </row>
     <row r="88" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="9"/>
       <c r="J88" s="9"/>
       <c r="L88" s="12"/>
-      <c r="N88" s="19"/>
+      <c r="N88" s="20"/>
     </row>
     <row r="89" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="9"/>
       <c r="J89" s="9"/>
       <c r="L89" s="12"/>
-      <c r="N89" s="19"/>
+      <c r="N89" s="20"/>
     </row>
     <row r="90" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="9"/>
       <c r="J90" s="9"/>
       <c r="L90" s="12"/>
-      <c r="N90" s="19"/>
+      <c r="N90" s="20"/>
     </row>
     <row r="91" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="9"/>
       <c r="J91" s="9"/>
       <c r="L91" s="12"/>
-      <c r="N91" s="19"/>
+      <c r="N91" s="20"/>
     </row>
     <row r="92" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="9"/>
       <c r="J92" s="9"/>
       <c r="L92" s="12"/>
-      <c r="N92" s="19"/>
+      <c r="N92" s="20"/>
     </row>
     <row r="93" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="9"/>
       <c r="J93" s="9"/>
       <c r="L93" s="12"/>
-      <c r="N93" s="19"/>
+      <c r="N93" s="20"/>
     </row>
     <row r="94" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="9"/>
       <c r="J94" s="9"/>
       <c r="L94" s="12"/>
-      <c r="N94" s="19"/>
+      <c r="N94" s="20"/>
     </row>
     <row r="95" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="9"/>
       <c r="J95" s="9"/>
       <c r="L95" s="12"/>
-      <c r="N95" s="19"/>
+      <c r="N95" s="20"/>
     </row>
     <row r="96" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="9"/>
       <c r="J96" s="9"/>
       <c r="L96" s="12"/>
-      <c r="N96" s="19"/>
+      <c r="N96" s="20"/>
     </row>
     <row r="97" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="9"/>
       <c r="J97" s="9"/>
       <c r="L97" s="12"/>
-      <c r="N97" s="19"/>
+      <c r="N97" s="20"/>
     </row>
     <row r="98" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="9"/>
       <c r="J98" s="9"/>
       <c r="L98" s="12"/>
-      <c r="N98" s="19"/>
+      <c r="N98" s="20"/>
     </row>
     <row r="99" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="9"/>
       <c r="J99" s="9"/>
       <c r="L99" s="12"/>
-      <c r="N99" s="19"/>
+      <c r="N99" s="20"/>
     </row>
     <row r="100" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="9"/>
       <c r="J100" s="9"/>
       <c r="L100" s="12"/>
-      <c r="N100" s="19"/>
+      <c r="N100" s="20"/>
     </row>
     <row r="101" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="9"/>
       <c r="J101" s="9"/>
       <c r="L101" s="12"/>
-      <c r="N101" s="19"/>
+      <c r="N101" s="20"/>
     </row>
     <row r="102" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="9"/>
       <c r="J102" s="9"/>
       <c r="L102" s="12"/>
-      <c r="N102" s="19"/>
+      <c r="N102" s="20"/>
     </row>
     <row r="103" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="9"/>
       <c r="J103" s="9"/>
       <c r="L103" s="12"/>
-      <c r="N103" s="19"/>
+      <c r="N103" s="20"/>
     </row>
     <row r="104" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="9"/>
       <c r="J104" s="9"/>
       <c r="L104" s="12"/>
-      <c r="N104" s="19"/>
+      <c r="N104" s="20"/>
     </row>
     <row r="105" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="9"/>
       <c r="J105" s="9"/>
       <c r="L105" s="12"/>
-      <c r="N105" s="19"/>
+      <c r="N105" s="20"/>
     </row>
     <row r="106" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="9"/>
       <c r="J106" s="9"/>
       <c r="L106" s="12"/>
-      <c r="N106" s="19"/>
+      <c r="N106" s="20"/>
     </row>
     <row r="107" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="9"/>
       <c r="J107" s="9"/>
       <c r="L107" s="12"/>
-      <c r="N107" s="19"/>
+      <c r="N107" s="20"/>
     </row>
     <row r="108" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="9"/>
       <c r="J108" s="9"/>
       <c r="L108" s="12"/>
-      <c r="N108" s="19"/>
+      <c r="N108" s="20"/>
     </row>
     <row r="109" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="9"/>
       <c r="J109" s="9"/>
       <c r="L109" s="12"/>
-      <c r="N109" s="19"/>
+      <c r="N109" s="20"/>
     </row>
     <row r="110" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="9"/>
       <c r="J110" s="9"/>
       <c r="L110" s="12"/>
-      <c r="N110" s="19"/>
+      <c r="N110" s="20"/>
     </row>
     <row r="111" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="9"/>
       <c r="J111" s="9"/>
       <c r="L111" s="12"/>
-      <c r="N111" s="19"/>
+      <c r="N111" s="20"/>
     </row>
     <row r="112" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="9"/>
       <c r="J112" s="9"/>
       <c r="L112" s="12"/>
-      <c r="N112" s="19"/>
+      <c r="N112" s="20"/>
     </row>
     <row r="113" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="9"/>
       <c r="J113" s="9"/>
       <c r="L113" s="12"/>
-      <c r="N113" s="19"/>
+      <c r="N113" s="20"/>
     </row>
     <row r="114" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="9"/>
       <c r="J114" s="9"/>
       <c r="L114" s="12"/>
-      <c r="N114" s="19"/>
+      <c r="N114" s="20"/>
     </row>
     <row r="115" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="9"/>
       <c r="J115" s="9"/>
       <c r="L115" s="12"/>
-      <c r="N115" s="19"/>
+      <c r="N115" s="20"/>
     </row>
     <row r="116" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="9"/>
       <c r="J116" s="9"/>
       <c r="L116" s="12"/>
-      <c r="N116" s="19"/>
+      <c r="N116" s="20"/>
     </row>
     <row r="117" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="9"/>
       <c r="J117" s="9"/>
       <c r="L117" s="12"/>
-      <c r="N117" s="19"/>
+      <c r="N117" s="20"/>
     </row>
     <row r="118" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="9"/>
       <c r="J118" s="9"/>
       <c r="L118" s="12"/>
-      <c r="N118" s="19"/>
+      <c r="N118" s="20"/>
     </row>
     <row r="119" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="9"/>
       <c r="J119" s="9"/>
       <c r="L119" s="12"/>
-      <c r="N119" s="19"/>
+      <c r="N119" s="20"/>
     </row>
     <row r="120" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="9"/>
       <c r="J120" s="9"/>
       <c r="L120" s="12"/>
-      <c r="N120" s="19"/>
+      <c r="N120" s="20"/>
     </row>
     <row r="121" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="9"/>
       <c r="J121" s="9"/>
       <c r="L121" s="12"/>
-      <c r="N121" s="19"/>
+      <c r="N121" s="20"/>
     </row>
     <row r="122" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="9"/>
       <c r="J122" s="9"/>
       <c r="L122" s="12"/>
-      <c r="N122" s="19"/>
+      <c r="N122" s="20"/>
     </row>
     <row r="123" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="9"/>
       <c r="J123" s="9"/>
       <c r="L123" s="12"/>
-      <c r="N123" s="19"/>
+      <c r="N123" s="20"/>
     </row>
     <row r="124" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="9"/>
       <c r="J124" s="9"/>
       <c r="L124" s="12"/>
-      <c r="N124" s="19"/>
+      <c r="N124" s="20"/>
     </row>
     <row r="125" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="9"/>
       <c r="J125" s="9"/>
       <c r="L125" s="12"/>
-      <c r="N125" s="19"/>
+      <c r="N125" s="20"/>
     </row>
     <row r="126" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="9"/>
       <c r="J126" s="9"/>
       <c r="L126" s="12"/>
-      <c r="N126" s="19"/>
+      <c r="N126" s="20"/>
     </row>
     <row r="127" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="9"/>
       <c r="J127" s="9"/>
       <c r="L127" s="12"/>
-      <c r="N127" s="19"/>
+      <c r="N127" s="20"/>
     </row>
     <row r="128" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="9"/>
       <c r="J128" s="9"/>
       <c r="L128" s="12"/>
-      <c r="N128" s="19"/>
+      <c r="N128" s="20"/>
     </row>
     <row r="129" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="9"/>
       <c r="J129" s="9"/>
       <c r="L129" s="12"/>
-      <c r="N129" s="19"/>
+      <c r="N129" s="20"/>
     </row>
     <row r="130" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="9"/>
       <c r="J130" s="9"/>
       <c r="L130" s="12"/>
-      <c r="N130" s="19"/>
+      <c r="N130" s="20"/>
     </row>
     <row r="131" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="9"/>
       <c r="J131" s="9"/>
       <c r="L131" s="12"/>
-      <c r="N131" s="19"/>
+      <c r="N131" s="20"/>
     </row>
     <row r="132" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="9"/>
       <c r="J132" s="9"/>
       <c r="L132" s="12"/>
-      <c r="N132" s="19"/>
+      <c r="N132" s="20"/>
     </row>
     <row r="133" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="9"/>
       <c r="J133" s="9"/>
       <c r="L133" s="12"/>
-      <c r="N133" s="19"/>
+      <c r="N133" s="20"/>
     </row>
     <row r="134" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="9"/>
       <c r="J134" s="9"/>
       <c r="L134" s="12"/>
-      <c r="N134" s="19"/>
+      <c r="N134" s="20"/>
     </row>
     <row r="135" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="9"/>
       <c r="J135" s="9"/>
       <c r="L135" s="12"/>
-      <c r="N135" s="19"/>
+      <c r="N135" s="20"/>
     </row>
     <row r="136" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="9"/>
       <c r="J136" s="9"/>
       <c r="L136" s="12"/>
-      <c r="N136" s="19"/>
+      <c r="N136" s="20"/>
     </row>
     <row r="137" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="9"/>
       <c r="J137" s="9"/>
       <c r="L137" s="12"/>
-      <c r="N137" s="19"/>
+      <c r="N137" s="20"/>
     </row>
     <row r="138" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="9"/>
       <c r="J138" s="9"/>
       <c r="L138" s="12"/>
-      <c r="N138" s="19"/>
+      <c r="N138" s="20"/>
     </row>
     <row r="139" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="9"/>
       <c r="J139" s="9"/>
       <c r="L139" s="12"/>
-      <c r="N139" s="19"/>
+      <c r="N139" s="20"/>
     </row>
     <row r="140" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="9"/>
       <c r="J140" s="9"/>
       <c r="L140" s="12"/>
-      <c r="N140" s="19"/>
+      <c r="N140" s="20"/>
     </row>
     <row r="141" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="9"/>
       <c r="J141" s="9"/>
       <c r="L141" s="12"/>
-      <c r="N141" s="19"/>
+      <c r="N141" s="20"/>
     </row>
     <row r="142" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="9"/>
       <c r="J142" s="9"/>
       <c r="L142" s="12"/>
-      <c r="N142" s="19"/>
+      <c r="N142" s="20"/>
     </row>
     <row r="143" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="9"/>
       <c r="J143" s="9"/>
       <c r="L143" s="12"/>
-      <c r="N143" s="19"/>
+      <c r="N143" s="20"/>
     </row>
     <row r="144" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="9"/>
       <c r="J144" s="9"/>
       <c r="L144" s="12"/>
-      <c r="N144" s="19"/>
+      <c r="N144" s="20"/>
     </row>
     <row r="145" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="9"/>
       <c r="J145" s="9"/>
       <c r="L145" s="12"/>
-      <c r="N145" s="19"/>
+      <c r="N145" s="20"/>
     </row>
     <row r="146" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="9"/>
       <c r="J146" s="9"/>
       <c r="L146" s="12"/>
-      <c r="N146" s="19"/>
+      <c r="N146" s="20"/>
     </row>
     <row r="147" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="9"/>
       <c r="J147" s="9"/>
       <c r="L147" s="12"/>
-      <c r="N147" s="19"/>
+      <c r="N147" s="20"/>
     </row>
     <row r="148" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="9"/>
       <c r="J148" s="9"/>
       <c r="L148" s="12"/>
-      <c r="N148" s="19"/>
+      <c r="N148" s="20"/>
     </row>
     <row r="149" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="9"/>
       <c r="J149" s="9"/>
       <c r="L149" s="12"/>
-      <c r="N149" s="19"/>
+      <c r="N149" s="20"/>
     </row>
     <row r="150" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="9"/>
       <c r="J150" s="9"/>
       <c r="L150" s="12"/>
-      <c r="N150" s="19"/>
+      <c r="N150" s="20"/>
     </row>
     <row r="151" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="9"/>
       <c r="J151" s="9"/>
       <c r="L151" s="12"/>
-      <c r="N151" s="19"/>
+      <c r="N151" s="20"/>
     </row>
     <row r="152" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="9"/>
       <c r="J152" s="9"/>
       <c r="L152" s="12"/>
-      <c r="N152" s="19"/>
+      <c r="N152" s="20"/>
     </row>
     <row r="153" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="9"/>
       <c r="J153" s="9"/>
       <c r="L153" s="12"/>
-      <c r="N153" s="19"/>
+      <c r="N153" s="20"/>
     </row>
     <row r="154" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="9"/>
       <c r="J154" s="9"/>
       <c r="L154" s="12"/>
-      <c r="N154" s="19"/>
+      <c r="N154" s="20"/>
     </row>
     <row r="155" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="9"/>
       <c r="J155" s="9"/>
       <c r="L155" s="12"/>
-      <c r="N155" s="19"/>
+      <c r="N155" s="20"/>
     </row>
     <row r="156" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="9"/>
       <c r="J156" s="9"/>
       <c r="L156" s="12"/>
-      <c r="N156" s="19"/>
+      <c r="N156" s="20"/>
     </row>
     <row r="157" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="9"/>
       <c r="J157" s="9"/>
       <c r="L157" s="12"/>
-      <c r="N157" s="19"/>
+      <c r="N157" s="20"/>
     </row>
     <row r="158" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="9"/>
       <c r="J158" s="9"/>
       <c r="L158" s="12"/>
-      <c r="N158" s="19"/>
+      <c r="N158" s="20"/>
     </row>
     <row r="159" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="9"/>
       <c r="J159" s="9"/>
       <c r="L159" s="12"/>
-      <c r="N159" s="19"/>
+      <c r="N159" s="20"/>
     </row>
     <row r="160" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="9"/>
       <c r="J160" s="9"/>
       <c r="L160" s="12"/>
-      <c r="N160" s="19"/>
+      <c r="N160" s="20"/>
     </row>
     <row r="161" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="9"/>
       <c r="J161" s="9"/>
       <c r="L161" s="12"/>
-      <c r="N161" s="19"/>
+      <c r="N161" s="20"/>
     </row>
     <row r="162" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="9"/>
       <c r="J162" s="9"/>
       <c r="L162" s="12"/>
-      <c r="N162" s="19"/>
+      <c r="N162" s="20"/>
     </row>
     <row r="163" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="9"/>
       <c r="J163" s="9"/>
       <c r="L163" s="12"/>
-      <c r="N163" s="19"/>
+      <c r="N163" s="20"/>
     </row>
     <row r="164" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="9"/>
       <c r="J164" s="9"/>
       <c r="L164" s="12"/>
-      <c r="N164" s="19"/>
+      <c r="N164" s="20"/>
     </row>
     <row r="165" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="9"/>
       <c r="J165" s="9"/>
       <c r="L165" s="12"/>
-      <c r="N165" s="19"/>
+      <c r="N165" s="20"/>
     </row>
     <row r="166" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="9"/>
       <c r="J166" s="9"/>
       <c r="L166" s="12"/>
-      <c r="N166" s="19"/>
+      <c r="N166" s="20"/>
     </row>
     <row r="167" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="9"/>
       <c r="J167" s="9"/>
       <c r="L167" s="12"/>
-      <c r="N167" s="19"/>
+      <c r="N167" s="20"/>
     </row>
     <row r="168" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="9"/>
       <c r="J168" s="9"/>
       <c r="L168" s="12"/>
-      <c r="N168" s="19"/>
+      <c r="N168" s="20"/>
     </row>
     <row r="169" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="9"/>
       <c r="J169" s="9"/>
       <c r="L169" s="12"/>
-      <c r="N169" s="19"/>
+      <c r="N169" s="20"/>
     </row>
     <row r="170" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="9"/>
       <c r="J170" s="9"/>
       <c r="L170" s="12"/>
-      <c r="N170" s="19"/>
+      <c r="N170" s="20"/>
     </row>
     <row r="171" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="9"/>
       <c r="J171" s="9"/>
       <c r="L171" s="12"/>
-      <c r="N171" s="19"/>
+      <c r="N171" s="20"/>
     </row>
     <row r="172" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="9"/>
       <c r="J172" s="9"/>
       <c r="L172" s="12"/>
-      <c r="N172" s="19"/>
+      <c r="N172" s="20"/>
     </row>
     <row r="173" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="9"/>
       <c r="J173" s="9"/>
       <c r="L173" s="12"/>
-      <c r="N173" s="19"/>
+      <c r="N173" s="20"/>
     </row>
     <row r="174" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="9"/>
       <c r="J174" s="9"/>
       <c r="L174" s="12"/>
-      <c r="N174" s="19"/>
+      <c r="N174" s="20"/>
     </row>
     <row r="175" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="9"/>
       <c r="J175" s="9"/>
       <c r="L175" s="12"/>
-      <c r="N175" s="19"/>
+      <c r="N175" s="20"/>
     </row>
     <row r="176" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="9"/>
       <c r="J176" s="9"/>
       <c r="L176" s="12"/>
-      <c r="N176" s="19"/>
+      <c r="N176" s="20"/>
     </row>
     <row r="177" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="9"/>
       <c r="J177" s="9"/>
       <c r="L177" s="12"/>
-      <c r="N177" s="19"/>
+      <c r="N177" s="20"/>
     </row>
     <row r="178" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="9"/>
       <c r="J178" s="9"/>
       <c r="L178" s="12"/>
-      <c r="N178" s="19"/>
+      <c r="N178" s="20"/>
     </row>
     <row r="179" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="9"/>
       <c r="J179" s="9"/>
       <c r="L179" s="12"/>
-      <c r="N179" s="19"/>
+      <c r="N179" s="20"/>
     </row>
     <row r="180" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="9"/>
       <c r="J180" s="9"/>
       <c r="L180" s="12"/>
-      <c r="N180" s="19"/>
+      <c r="N180" s="20"/>
     </row>
     <row r="181" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="9"/>
       <c r="J181" s="9"/>
       <c r="L181" s="12"/>
-      <c r="N181" s="19"/>
+      <c r="N181" s="20"/>
     </row>
     <row r="182" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="9"/>
       <c r="J182" s="9"/>
       <c r="L182" s="12"/>
-      <c r="N182" s="19"/>
+      <c r="N182" s="20"/>
     </row>
     <row r="183" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="9"/>
       <c r="J183" s="9"/>
       <c r="L183" s="12"/>
-      <c r="N183" s="19"/>
+      <c r="N183" s="20"/>
     </row>
     <row r="184" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="9"/>
       <c r="J184" s="9"/>
       <c r="L184" s="12"/>
-      <c r="N184" s="19"/>
+      <c r="N184" s="20"/>
     </row>
     <row r="185" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="9"/>
       <c r="J185" s="9"/>
       <c r="L185" s="12"/>
-      <c r="N185" s="19"/>
+      <c r="N185" s="20"/>
     </row>
     <row r="186" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="9"/>
       <c r="J186" s="9"/>
       <c r="L186" s="12"/>
-      <c r="N186" s="19"/>
+      <c r="N186" s="20"/>
     </row>
     <row r="187" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="9"/>
       <c r="J187" s="9"/>
       <c r="L187" s="12"/>
-      <c r="N187" s="19"/>
+      <c r="N187" s="20"/>
     </row>
     <row r="188" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="9"/>
       <c r="J188" s="9"/>
       <c r="L188" s="12"/>
-      <c r="N188" s="19"/>
+      <c r="N188" s="20"/>
     </row>
     <row r="189" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="9"/>
       <c r="J189" s="9"/>
       <c r="L189" s="12"/>
-      <c r="N189" s="19"/>
+      <c r="N189" s="20"/>
     </row>
     <row r="190" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="9"/>
       <c r="J190" s="9"/>
       <c r="L190" s="12"/>
-      <c r="N190" s="19"/>
+      <c r="N190" s="20"/>
     </row>
     <row r="191" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="9"/>
       <c r="J191" s="9"/>
       <c r="L191" s="12"/>
-      <c r="N191" s="19"/>
+      <c r="N191" s="20"/>
     </row>
     <row r="192" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="9"/>
       <c r="J192" s="9"/>
       <c r="L192" s="12"/>
-      <c r="N192" s="19"/>
+      <c r="N192" s="20"/>
     </row>
     <row r="193" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="9"/>
       <c r="J193" s="9"/>
       <c r="L193" s="12"/>
-      <c r="N193" s="19"/>
+      <c r="N193" s="20"/>
     </row>
     <row r="194" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="9"/>
       <c r="J194" s="9"/>
       <c r="L194" s="12"/>
-      <c r="N194" s="19"/>
+      <c r="N194" s="20"/>
     </row>
     <row r="195" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="9"/>
       <c r="J195" s="9"/>
       <c r="L195" s="12"/>
-      <c r="N195" s="19"/>
+      <c r="N195" s="20"/>
     </row>
     <row r="196" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="9"/>
       <c r="J196" s="9"/>
       <c r="L196" s="12"/>
-      <c r="N196" s="19"/>
+      <c r="N196" s="20"/>
     </row>
     <row r="197" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="9"/>
       <c r="J197" s="9"/>
       <c r="L197" s="12"/>
-      <c r="N197" s="19"/>
+      <c r="N197" s="20"/>
     </row>
     <row r="198" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="9"/>
       <c r="J198" s="9"/>
       <c r="L198" s="12"/>
-      <c r="N198" s="19"/>
+      <c r="N198" s="20"/>
     </row>
     <row r="199" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="9"/>
       <c r="J199" s="9"/>
       <c r="L199" s="12"/>
-      <c r="N199" s="19"/>
+      <c r="N199" s="20"/>
     </row>
     <row r="200" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="9"/>
       <c r="J200" s="9"/>
       <c r="L200" s="12"/>
-      <c r="N200" s="19"/>
+      <c r="N200" s="20"/>
     </row>
     <row r="201" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="9"/>
       <c r="J201" s="9"/>
       <c r="L201" s="12"/>
-      <c r="N201" s="19"/>
+      <c r="N201" s="20"/>
     </row>
     <row r="202" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="9"/>
       <c r="J202" s="9"/>
       <c r="L202" s="12"/>
-      <c r="N202" s="19"/>
+      <c r="N202" s="20"/>
     </row>
     <row r="203" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="9"/>
       <c r="J203" s="9"/>
       <c r="L203" s="12"/>
-      <c r="N203" s="19"/>
+      <c r="N203" s="20"/>
     </row>
     <row r="204" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="9"/>
       <c r="J204" s="9"/>
       <c r="L204" s="12"/>
-      <c r="N204" s="19"/>
+      <c r="N204" s="20"/>
     </row>
     <row r="205" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="9"/>
       <c r="J205" s="9"/>
       <c r="L205" s="12"/>
-      <c r="N205" s="19"/>
+      <c r="N205" s="20"/>
     </row>
     <row r="206" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="9"/>
       <c r="J206" s="9"/>
       <c r="L206" s="12"/>
-      <c r="N206" s="19"/>
+      <c r="N206" s="20"/>
     </row>
     <row r="207" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="9"/>
       <c r="J207" s="9"/>
       <c r="L207" s="12"/>
-      <c r="N207" s="19"/>
+      <c r="N207" s="20"/>
     </row>
     <row r="208" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="9"/>
       <c r="J208" s="9"/>
       <c r="L208" s="12"/>
-      <c r="N208" s="19"/>
+      <c r="N208" s="20"/>
     </row>
     <row r="209" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="9"/>
       <c r="J209" s="9"/>
       <c r="L209" s="12"/>
-      <c r="N209" s="19"/>
+      <c r="N209" s="20"/>
     </row>
     <row r="210" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="9"/>
       <c r="J210" s="9"/>
       <c r="L210" s="12"/>
-      <c r="N210" s="19"/>
+      <c r="N210" s="20"/>
     </row>
     <row r="211" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="9"/>
       <c r="J211" s="9"/>
       <c r="L211" s="12"/>
-      <c r="N211" s="19"/>
+      <c r="N211" s="20"/>
     </row>
     <row r="212" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="9"/>
       <c r="J212" s="9"/>
       <c r="L212" s="12"/>
-      <c r="N212" s="19"/>
+      <c r="N212" s="20"/>
     </row>
     <row r="213" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="9"/>
       <c r="J213" s="9"/>
       <c r="L213" s="12"/>
-      <c r="N213" s="19"/>
+      <c r="N213" s="20"/>
     </row>
     <row r="214" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="9"/>
       <c r="J214" s="9"/>
       <c r="L214" s="12"/>
-      <c r="N214" s="19"/>
+      <c r="N214" s="20"/>
     </row>
     <row r="215" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="9"/>
       <c r="J215" s="9"/>
       <c r="L215" s="12"/>
-      <c r="N215" s="19"/>
+      <c r="N215" s="20"/>
     </row>
     <row r="216" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="9"/>
       <c r="J216" s="9"/>
       <c r="L216" s="12"/>
-      <c r="N216" s="19"/>
+      <c r="N216" s="20"/>
     </row>
     <row r="217" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="9"/>
       <c r="J217" s="9"/>
       <c r="L217" s="12"/>
-      <c r="N217" s="19"/>
+      <c r="N217" s="20"/>
     </row>
     <row r="218" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="9"/>
       <c r="J218" s="9"/>
       <c r="L218" s="12"/>
-      <c r="N218" s="19"/>
+      <c r="N218" s="20"/>
     </row>
     <row r="219" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="9"/>
       <c r="J219" s="9"/>
       <c r="L219" s="12"/>
-      <c r="N219" s="19"/>
+      <c r="N219" s="20"/>
     </row>
     <row r="220" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="9"/>
       <c r="J220" s="9"/>
       <c r="L220" s="12"/>
-      <c r="N220" s="19"/>
+      <c r="N220" s="20"/>
     </row>
     <row r="221" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="9"/>
       <c r="J221" s="9"/>
       <c r="L221" s="12"/>
-      <c r="N221" s="19"/>
+      <c r="N221" s="20"/>
     </row>
     <row r="222" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="9"/>
       <c r="J222" s="9"/>
       <c r="L222" s="12"/>
-      <c r="N222" s="19"/>
+      <c r="N222" s="20"/>
     </row>
     <row r="223" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="9"/>
       <c r="J223" s="9"/>
       <c r="L223" s="12"/>
-      <c r="N223" s="19"/>
+      <c r="N223" s="20"/>
     </row>
     <row r="224" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="9"/>
       <c r="J224" s="9"/>
       <c r="L224" s="12"/>
-      <c r="N224" s="19"/>
+      <c r="N224" s="20"/>
     </row>
     <row r="225" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="9"/>
       <c r="J225" s="9"/>
       <c r="L225" s="12"/>
-      <c r="N225" s="19"/>
+      <c r="N225" s="20"/>
     </row>
     <row r="226" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="9"/>
       <c r="J226" s="9"/>
       <c r="L226" s="12"/>
-      <c r="N226" s="19"/>
+      <c r="N226" s="20"/>
     </row>
     <row r="227" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="9"/>
       <c r="J227" s="9"/>
       <c r="L227" s="12"/>
-      <c r="N227" s="19"/>
+      <c r="N227" s="20"/>
     </row>
     <row r="228" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="9"/>
       <c r="J228" s="9"/>
       <c r="L228" s="12"/>
-      <c r="N228" s="19"/>
+      <c r="N228" s="20"/>
     </row>
     <row r="229" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="9"/>
       <c r="J229" s="9"/>
       <c r="L229" s="12"/>
-      <c r="N229" s="19"/>
+      <c r="N229" s="20"/>
     </row>
     <row r="230" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="9"/>
       <c r="J230" s="9"/>
       <c r="L230" s="12"/>
-      <c r="N230" s="19"/>
+      <c r="N230" s="20"/>
     </row>
     <row r="231" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="9"/>
       <c r="J231" s="9"/>
       <c r="L231" s="12"/>
-      <c r="N231" s="19"/>
+      <c r="N231" s="20"/>
     </row>
     <row r="232" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="9"/>
       <c r="J232" s="9"/>
       <c r="L232" s="12"/>
-      <c r="N232" s="19"/>
+      <c r="N232" s="20"/>
     </row>
     <row r="233" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="9"/>
       <c r="J233" s="9"/>
       <c r="L233" s="12"/>
-      <c r="N233" s="19"/>
+      <c r="N233" s="20"/>
     </row>
     <row r="234" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="9"/>
       <c r="J234" s="9"/>
       <c r="L234" s="12"/>
-      <c r="N234" s="19"/>
+      <c r="N234" s="20"/>
     </row>
     <row r="235" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="9"/>
       <c r="J235" s="9"/>
       <c r="L235" s="12"/>
-      <c r="N235" s="19"/>
+      <c r="N235" s="20"/>
     </row>
     <row r="236" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="9"/>
       <c r="J236" s="9"/>
       <c r="L236" s="12"/>
-      <c r="N236" s="19"/>
+      <c r="N236" s="20"/>
     </row>
     <row r="237" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="9"/>
       <c r="J237" s="9"/>
       <c r="L237" s="12"/>
-      <c r="N237" s="19"/>
+      <c r="N237" s="20"/>
     </row>
     <row r="238" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="9"/>
       <c r="J238" s="9"/>
       <c r="L238" s="12"/>
-      <c r="N238" s="19"/>
+      <c r="N238" s="20"/>
     </row>
     <row r="239" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="9"/>
       <c r="J239" s="9"/>
       <c r="L239" s="12"/>
-      <c r="N239" s="19"/>
+      <c r="N239" s="20"/>
     </row>
     <row r="240" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="9"/>
       <c r="J240" s="9"/>
       <c r="L240" s="12"/>
-      <c r="N240" s="19"/>
+      <c r="N240" s="20"/>
     </row>
     <row r="241" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="9"/>
       <c r="J241" s="9"/>
       <c r="L241" s="12"/>
-      <c r="N241" s="19"/>
+      <c r="N241" s="20"/>
     </row>
     <row r="242" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="9"/>
       <c r="J242" s="9"/>
       <c r="L242" s="12"/>
-      <c r="N242" s="19"/>
+      <c r="N242" s="20"/>
     </row>
     <row r="243" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="9"/>
       <c r="J243" s="9"/>
       <c r="L243" s="12"/>
-      <c r="N243" s="19"/>
+      <c r="N243" s="20"/>
     </row>
     <row r="244" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="9"/>
       <c r="J244" s="9"/>
       <c r="L244" s="12"/>
-      <c r="N244" s="19"/>
+      <c r="N244" s="20"/>
     </row>
     <row r="245" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="9"/>
       <c r="J245" s="9"/>
       <c r="L245" s="12"/>
-      <c r="N245" s="19"/>
+      <c r="N245" s="20"/>
     </row>
     <row r="246" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="9"/>
       <c r="J246" s="9"/>
       <c r="L246" s="12"/>
-      <c r="N246" s="19"/>
+      <c r="N246" s="20"/>
     </row>
     <row r="247" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="9"/>
       <c r="J247" s="9"/>
       <c r="L247" s="12"/>
-      <c r="N247" s="19"/>
+      <c r="N247" s="20"/>
     </row>
     <row r="248" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="9"/>
       <c r="J248" s="9"/>
       <c r="L248" s="12"/>
-      <c r="N248" s="19"/>
+      <c r="N248" s="20"/>
     </row>
     <row r="249" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="9"/>
       <c r="J249" s="9"/>
       <c r="L249" s="12"/>
-      <c r="N249" s="19"/>
+      <c r="N249" s="20"/>
     </row>
     <row r="250" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="9"/>
       <c r="J250" s="9"/>
       <c r="L250" s="12"/>
-      <c r="N250" s="19"/>
+      <c r="N250" s="20"/>
     </row>
     <row r="251" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="9"/>
       <c r="J251" s="9"/>
       <c r="L251" s="12"/>
-      <c r="N251" s="19"/>
+      <c r="N251" s="20"/>
     </row>
     <row r="252" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="9"/>
       <c r="J252" s="9"/>
       <c r="L252" s="12"/>
-      <c r="N252" s="19"/>
+      <c r="N252" s="20"/>
     </row>
     <row r="253" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="9"/>
       <c r="J253" s="9"/>
       <c r="L253" s="12"/>
-      <c r="N253" s="19"/>
+      <c r="N253" s="20"/>
     </row>
     <row r="254" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="9"/>
       <c r="J254" s="9"/>
       <c r="L254" s="12"/>
-      <c r="N254" s="19"/>
+      <c r="N254" s="20"/>
     </row>
     <row r="255" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="9"/>
       <c r="J255" s="9"/>
       <c r="L255" s="12"/>
-      <c r="N255" s="19"/>
+      <c r="N255" s="20"/>
     </row>
     <row r="256" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="9"/>
       <c r="J256" s="9"/>
       <c r="L256" s="12"/>
-      <c r="N256" s="19"/>
+      <c r="N256" s="20"/>
     </row>
     <row r="257" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="9"/>
       <c r="J257" s="9"/>
       <c r="L257" s="12"/>
-      <c r="N257" s="19"/>
+      <c r="N257" s="20"/>
     </row>
     <row r="258" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="9"/>
       <c r="J258" s="9"/>
       <c r="L258" s="12"/>
-      <c r="N258" s="19"/>
+      <c r="N258" s="20"/>
     </row>
     <row r="259" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="9"/>
       <c r="J259" s="9"/>
       <c r="L259" s="12"/>
-      <c r="N259" s="19"/>
+      <c r="N259" s="20"/>
     </row>
     <row r="260" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="9"/>
       <c r="J260" s="9"/>
       <c r="L260" s="12"/>
-      <c r="N260" s="19"/>
+      <c r="N260" s="20"/>
     </row>
     <row r="261" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="9"/>
       <c r="J261" s="9"/>
       <c r="L261" s="12"/>
-      <c r="N261" s="19"/>
+      <c r="N261" s="20"/>
     </row>
     <row r="262" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="9"/>
       <c r="J262" s="9"/>
       <c r="L262" s="12"/>
-      <c r="N262" s="19"/>
+      <c r="N262" s="20"/>
     </row>
     <row r="263" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="9"/>
       <c r="J263" s="9"/>
       <c r="L263" s="12"/>
-      <c r="N263" s="19"/>
+      <c r="N263" s="20"/>
     </row>
     <row r="264" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="9"/>
       <c r="J264" s="9"/>
       <c r="L264" s="12"/>
-      <c r="N264" s="19"/>
+      <c r="N264" s="20"/>
     </row>
     <row r="265" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="9"/>
       <c r="J265" s="9"/>
       <c r="L265" s="12"/>
-      <c r="N265" s="19"/>
+      <c r="N265" s="20"/>
     </row>
     <row r="266" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="9"/>
       <c r="J266" s="9"/>
       <c r="L266" s="12"/>
-      <c r="N266" s="19"/>
+      <c r="N266" s="20"/>
     </row>
     <row r="267" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="9"/>
       <c r="J267" s="9"/>
       <c r="L267" s="12"/>
-      <c r="N267" s="19"/>
+      <c r="N267" s="20"/>
     </row>
     <row r="268" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="9"/>
       <c r="J268" s="9"/>
       <c r="L268" s="12"/>
-      <c r="N268" s="19"/>
+      <c r="N268" s="20"/>
     </row>
     <row r="269" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="9"/>
       <c r="J269" s="9"/>
       <c r="L269" s="12"/>
-      <c r="N269" s="19"/>
+      <c r="N269" s="20"/>
     </row>
     <row r="270" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="9"/>
       <c r="J270" s="9"/>
       <c r="L270" s="12"/>
-      <c r="N270" s="19"/>
+      <c r="N270" s="20"/>
     </row>
     <row r="271" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="9"/>
       <c r="J271" s="9"/>
       <c r="L271" s="12"/>
-      <c r="N271" s="19"/>
+      <c r="N271" s="20"/>
     </row>
     <row r="272" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="9"/>
       <c r="J272" s="9"/>
       <c r="L272" s="12"/>
-      <c r="N272" s="19"/>
+      <c r="N272" s="20"/>
     </row>
     <row r="273" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="9"/>
       <c r="J273" s="9"/>
       <c r="L273" s="12"/>
-      <c r="N273" s="19"/>
+      <c r="N273" s="20"/>
     </row>
     <row r="274" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="9"/>
       <c r="J274" s="9"/>
       <c r="L274" s="12"/>
-      <c r="N274" s="19"/>
+      <c r="N274" s="20"/>
     </row>
     <row r="275" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="9"/>
       <c r="J275" s="9"/>
       <c r="L275" s="12"/>
-      <c r="N275" s="19"/>
+      <c r="N275" s="20"/>
     </row>
     <row r="276" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="9"/>
       <c r="J276" s="9"/>
       <c r="L276" s="12"/>
-      <c r="N276" s="19"/>
+      <c r="N276" s="20"/>
     </row>
     <row r="277" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="9"/>
       <c r="J277" s="9"/>
       <c r="L277" s="12"/>
-      <c r="N277" s="19"/>
+      <c r="N277" s="20"/>
     </row>
     <row r="278" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="9"/>
       <c r="J278" s="9"/>
       <c r="L278" s="12"/>
-      <c r="N278" s="19"/>
+      <c r="N278" s="20"/>
     </row>
     <row r="279" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="9"/>
       <c r="J279" s="9"/>
       <c r="L279" s="12"/>
-      <c r="N279" s="19"/>
+      <c r="N279" s="20"/>
     </row>
     <row r="280" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="9"/>
       <c r="J280" s="9"/>
       <c r="L280" s="12"/>
-      <c r="N280" s="19"/>
+      <c r="N280" s="20"/>
     </row>
     <row r="281" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="9"/>
       <c r="J281" s="9"/>
       <c r="L281" s="12"/>
-      <c r="N281" s="19"/>
+      <c r="N281" s="20"/>
     </row>
     <row r="282" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="9"/>
       <c r="J282" s="9"/>
       <c r="L282" s="12"/>
-      <c r="N282" s="19"/>
+      <c r="N282" s="20"/>
     </row>
     <row r="283" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="9"/>
       <c r="J283" s="9"/>
       <c r="L283" s="12"/>
-      <c r="N283" s="19"/>
+      <c r="N283" s="20"/>
     </row>
     <row r="284" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="9"/>
       <c r="J284" s="9"/>
       <c r="L284" s="12"/>
-      <c r="N284" s="19"/>
+      <c r="N284" s="20"/>
     </row>
     <row r="285" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="9"/>
       <c r="J285" s="9"/>
       <c r="L285" s="12"/>
-      <c r="N285" s="19"/>
+      <c r="N285" s="20"/>
     </row>
     <row r="286" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="9"/>
       <c r="J286" s="9"/>
       <c r="L286" s="12"/>
-      <c r="N286" s="19"/>
+      <c r="N286" s="20"/>
     </row>
     <row r="287" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="9"/>
       <c r="J287" s="9"/>
       <c r="L287" s="12"/>
-      <c r="N287" s="19"/>
+      <c r="N287" s="20"/>
     </row>
     <row r="288" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="9"/>
       <c r="J288" s="9"/>
       <c r="L288" s="12"/>
-      <c r="N288" s="19"/>
+      <c r="N288" s="20"/>
     </row>
     <row r="289" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="9"/>
       <c r="J289" s="9"/>
       <c r="L289" s="12"/>
-      <c r="N289" s="19"/>
+      <c r="N289" s="20"/>
     </row>
     <row r="290" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="9"/>
       <c r="J290" s="9"/>
       <c r="L290" s="12"/>
-      <c r="N290" s="19"/>
+      <c r="N290" s="20"/>
     </row>
     <row r="291" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="9"/>
       <c r="J291" s="9"/>
       <c r="L291" s="12"/>
-      <c r="N291" s="19"/>
+      <c r="N291" s="20"/>
     </row>
     <row r="292" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="9"/>
       <c r="J292" s="9"/>
       <c r="L292" s="12"/>
-      <c r="N292" s="19"/>
+      <c r="N292" s="20"/>
     </row>
     <row r="293" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="9"/>
       <c r="J293" s="9"/>
       <c r="L293" s="12"/>
-      <c r="N293" s="19"/>
+      <c r="N293" s="20"/>
     </row>
     <row r="294" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="9"/>
       <c r="J294" s="9"/>
       <c r="L294" s="12"/>
-      <c r="N294" s="19"/>
+      <c r="N294" s="20"/>
     </row>
     <row r="295" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="9"/>
       <c r="J295" s="9"/>
       <c r="L295" s="12"/>
-      <c r="N295" s="19"/>
+      <c r="N295" s="20"/>
     </row>
     <row r="296" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A296" s="9"/>
       <c r="J296" s="9"/>
       <c r="L296" s="12"/>
-      <c r="N296" s="19"/>
+      <c r="N296" s="20"/>
     </row>
     <row r="297" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="9"/>
       <c r="J297" s="9"/>
       <c r="L297" s="12"/>
-      <c r="N297" s="19"/>
+      <c r="N297" s="20"/>
     </row>
     <row r="298" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="9"/>
       <c r="J298" s="9"/>
       <c r="L298" s="12"/>
-      <c r="N298" s="19"/>
+      <c r="N298" s="20"/>
     </row>
     <row r="299" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="9"/>
       <c r="J299" s="9"/>
       <c r="L299" s="12"/>
-      <c r="N299" s="19"/>
+      <c r="N299" s="20"/>
     </row>
     <row r="300" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A300" s="9"/>
       <c r="J300" s="9"/>
       <c r="L300" s="12"/>
-      <c r="N300" s="19"/>
+      <c r="N300" s="20"/>
     </row>
     <row r="301" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A301" s="9"/>
       <c r="J301" s="9"/>
       <c r="L301" s="12"/>
-      <c r="N301" s="19"/>
+      <c r="N301" s="20"/>
     </row>
     <row r="302" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="9"/>
       <c r="J302" s="9"/>
       <c r="L302" s="12"/>
-      <c r="N302" s="19"/>
+      <c r="N302" s="20"/>
     </row>
     <row r="303" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="9"/>
       <c r="J303" s="9"/>
       <c r="L303" s="12"/>
-      <c r="N303" s="19"/>
+      <c r="N303" s="20"/>
     </row>
     <row r="304" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A304" s="9"/>
       <c r="J304" s="9"/>
       <c r="L304" s="12"/>
-      <c r="N304" s="19"/>
+      <c r="N304" s="20"/>
     </row>
     <row r="305" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A305" s="9"/>
       <c r="J305" s="9"/>
       <c r="L305" s="12"/>
-      <c r="N305" s="19"/>
+      <c r="N305" s="20"/>
     </row>
     <row r="306" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A306" s="9"/>
       <c r="J306" s="9"/>
       <c r="L306" s="12"/>
-      <c r="N306" s="19"/>
+      <c r="N306" s="20"/>
     </row>
     <row r="307" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A307" s="9"/>
       <c r="J307" s="9"/>
       <c r="L307" s="12"/>
-      <c r="N307" s="19"/>
+      <c r="N307" s="20"/>
     </row>
     <row r="308" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A308" s="9"/>
       <c r="J308" s="9"/>
       <c r="L308" s="12"/>
-      <c r="N308" s="19"/>
+      <c r="N308" s="20"/>
     </row>
     <row r="309" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A309" s="9"/>
       <c r="J309" s="9"/>
       <c r="L309" s="12"/>
-      <c r="N309" s="19"/>
+      <c r="N309" s="20"/>
     </row>
     <row r="310" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A310" s="9"/>
       <c r="J310" s="9"/>
       <c r="L310" s="12"/>
-      <c r="N310" s="19"/>
+      <c r="N310" s="20"/>
     </row>
     <row r="311" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A311" s="9"/>
       <c r="J311" s="9"/>
       <c r="L311" s="12"/>
-      <c r="N311" s="19"/>
+      <c r="N311" s="20"/>
     </row>
     <row r="312" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A312" s="9"/>
       <c r="J312" s="9"/>
       <c r="L312" s="12"/>
-      <c r="N312" s="19"/>
+      <c r="N312" s="20"/>
     </row>
     <row r="313" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A313" s="9"/>
       <c r="J313" s="9"/>
       <c r="L313" s="12"/>
-      <c r="N313" s="19"/>
+      <c r="N313" s="20"/>
     </row>
     <row r="314" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A314" s="9"/>
       <c r="J314" s="9"/>
       <c r="L314" s="12"/>
-      <c r="N314" s="19"/>
+      <c r="N314" s="20"/>
     </row>
     <row r="315" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A315" s="9"/>
       <c r="J315" s="9"/>
       <c r="L315" s="12"/>
-      <c r="N315" s="19"/>
+      <c r="N315" s="20"/>
     </row>
     <row r="316" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A316" s="9"/>
       <c r="J316" s="9"/>
       <c r="L316" s="12"/>
-      <c r="N316" s="19"/>
+      <c r="N316" s="20"/>
     </row>
     <row r="317" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A317" s="9"/>
       <c r="J317" s="9"/>
       <c r="L317" s="12"/>
-      <c r="N317" s="19"/>
+      <c r="N317" s="20"/>
     </row>
     <row r="318" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A318" s="9"/>
       <c r="J318" s="9"/>
       <c r="L318" s="12"/>
-      <c r="N318" s="19"/>
+      <c r="N318" s="20"/>
     </row>
     <row r="319" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A319" s="9"/>
       <c r="J319" s="9"/>
       <c r="L319" s="12"/>
-      <c r="N319" s="19"/>
+      <c r="N319" s="20"/>
     </row>
     <row r="320" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A320" s="9"/>
       <c r="J320" s="9"/>
       <c r="L320" s="12"/>
-      <c r="N320" s="19"/>
+      <c r="N320" s="20"/>
     </row>
     <row r="321" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A321" s="9"/>
       <c r="J321" s="9"/>
       <c r="L321" s="12"/>
-      <c r="N321" s="19"/>
+      <c r="N321" s="20"/>
     </row>
     <row r="322" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A322" s="9"/>
       <c r="J322" s="9"/>
       <c r="L322" s="12"/>
-      <c r="N322" s="19"/>
+      <c r="N322" s="20"/>
     </row>
     <row r="323" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A323" s="9"/>
       <c r="J323" s="9"/>
       <c r="L323" s="12"/>
-      <c r="N323" s="19"/>
+      <c r="N323" s="20"/>
     </row>
     <row r="324" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A324" s="9"/>
       <c r="J324" s="9"/>
       <c r="L324" s="12"/>
-      <c r="N324" s="19"/>
+      <c r="N324" s="20"/>
     </row>
     <row r="325" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A325" s="9"/>
       <c r="J325" s="9"/>
       <c r="L325" s="12"/>
-      <c r="N325" s="19"/>
+      <c r="N325" s="20"/>
     </row>
     <row r="326" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A326" s="9"/>
       <c r="J326" s="9"/>
       <c r="L326" s="12"/>
-      <c r="N326" s="19"/>
+      <c r="N326" s="20"/>
     </row>
     <row r="327" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A327" s="9"/>
       <c r="J327" s="9"/>
       <c r="L327" s="12"/>
-      <c r="N327" s="19"/>
+      <c r="N327" s="20"/>
     </row>
     <row r="328" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A328" s="9"/>
       <c r="J328" s="9"/>
       <c r="L328" s="12"/>
-      <c r="N328" s="19"/>
+      <c r="N328" s="20"/>
     </row>
     <row r="329" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A329" s="9"/>
       <c r="J329" s="9"/>
       <c r="L329" s="12"/>
-      <c r="N329" s="19"/>
+      <c r="N329" s="20"/>
     </row>
     <row r="330" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A330" s="9"/>
       <c r="J330" s="9"/>
       <c r="L330" s="12"/>
-      <c r="N330" s="19"/>
+      <c r="N330" s="20"/>
     </row>
     <row r="331" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A331" s="9"/>
       <c r="J331" s="9"/>
       <c r="L331" s="12"/>
-      <c r="N331" s="19"/>
+      <c r="N331" s="20"/>
     </row>
     <row r="332" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="9"/>
       <c r="J332" s="9"/>
       <c r="L332" s="12"/>
-      <c r="N332" s="19"/>
+      <c r="N332" s="20"/>
     </row>
     <row r="333" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A333" s="9"/>
       <c r="J333" s="9"/>
       <c r="L333" s="12"/>
-      <c r="N333" s="19"/>
+      <c r="N333" s="20"/>
     </row>
     <row r="334" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A334" s="9"/>
       <c r="J334" s="9"/>
       <c r="L334" s="12"/>
-      <c r="N334" s="19"/>
+      <c r="N334" s="20"/>
     </row>
     <row r="335" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A335" s="9"/>
       <c r="J335" s="9"/>
       <c r="L335" s="12"/>
-      <c r="N335" s="19"/>
+      <c r="N335" s="20"/>
     </row>
     <row r="336" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A336" s="9"/>
       <c r="J336" s="9"/>
       <c r="L336" s="12"/>
-      <c r="N336" s="19"/>
+      <c r="N336" s="20"/>
     </row>
     <row r="337" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A337" s="9"/>
       <c r="J337" s="9"/>
       <c r="L337" s="12"/>
-      <c r="N337" s="19"/>
+      <c r="N337" s="20"/>
     </row>
     <row r="338" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A338" s="9"/>
       <c r="J338" s="9"/>
       <c r="L338" s="12"/>
-      <c r="N338" s="19"/>
+      <c r="N338" s="20"/>
     </row>
     <row r="339" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A339" s="9"/>
       <c r="J339" s="9"/>
       <c r="L339" s="12"/>
-      <c r="N339" s="19"/>
+      <c r="N339" s="20"/>
     </row>
     <row r="340" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A340" s="9"/>
       <c r="J340" s="9"/>
       <c r="L340" s="12"/>
-      <c r="N340" s="19"/>
+      <c r="N340" s="20"/>
     </row>
     <row r="341" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A341" s="9"/>
       <c r="J341" s="9"/>
       <c r="L341" s="12"/>
-      <c r="N341" s="19"/>
+      <c r="N341" s="20"/>
     </row>
     <row r="342" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A342" s="9"/>
       <c r="J342" s="9"/>
       <c r="L342" s="12"/>
-      <c r="N342" s="19"/>
+      <c r="N342" s="20"/>
     </row>
     <row r="343" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A343" s="9"/>
       <c r="J343" s="9"/>
       <c r="L343" s="12"/>
-      <c r="N343" s="19"/>
+      <c r="N343" s="20"/>
     </row>
     <row r="344" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A344" s="9"/>
       <c r="J344" s="9"/>
       <c r="L344" s="12"/>
-      <c r="N344" s="19"/>
+      <c r="N344" s="20"/>
     </row>
     <row r="345" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A345" s="9"/>
       <c r="J345" s="9"/>
       <c r="L345" s="12"/>
-      <c r="N345" s="19"/>
+      <c r="N345" s="20"/>
     </row>
     <row r="346" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A346" s="9"/>
       <c r="J346" s="9"/>
       <c r="L346" s="12"/>
-      <c r="N346" s="19"/>
+      <c r="N346" s="20"/>
     </row>
     <row r="347" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A347" s="9"/>
       <c r="J347" s="9"/>
       <c r="L347" s="12"/>
-      <c r="N347" s="19"/>
+      <c r="N347" s="20"/>
     </row>
     <row r="348" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A348" s="9"/>
       <c r="J348" s="9"/>
       <c r="L348" s="12"/>
-      <c r="N348" s="19"/>
+      <c r="N348" s="20"/>
     </row>
     <row r="349" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A349" s="9"/>
       <c r="J349" s="9"/>
       <c r="L349" s="12"/>
-      <c r="N349" s="19"/>
+      <c r="N349" s="20"/>
     </row>
     <row r="350" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A350" s="9"/>
       <c r="J350" s="9"/>
       <c r="L350" s="12"/>
-      <c r="N350" s="19"/>
+      <c r="N350" s="20"/>
     </row>
     <row r="351" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A351" s="9"/>
       <c r="J351" s="9"/>
       <c r="L351" s="12"/>
-      <c r="N351" s="19"/>
+      <c r="N351" s="20"/>
     </row>
     <row r="352" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A352" s="9"/>
       <c r="J352" s="9"/>
       <c r="L352" s="12"/>
-      <c r="N352" s="19"/>
+      <c r="N352" s="20"/>
     </row>
     <row r="353" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A353" s="9"/>
       <c r="J353" s="9"/>
       <c r="L353" s="12"/>
-      <c r="N353" s="19"/>
+      <c r="N353" s="20"/>
     </row>
     <row r="354" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A354" s="9"/>
       <c r="J354" s="9"/>
       <c r="L354" s="12"/>
-      <c r="N354" s="19"/>
+      <c r="N354" s="20"/>
     </row>
     <row r="355" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A355" s="9"/>
       <c r="J355" s="9"/>
       <c r="L355" s="12"/>
-      <c r="N355" s="19"/>
+      <c r="N355" s="20"/>
     </row>
     <row r="356" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A356" s="9"/>
       <c r="J356" s="9"/>
       <c r="L356" s="12"/>
-      <c r="N356" s="19"/>
+      <c r="N356" s="20"/>
     </row>
     <row r="357" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A357" s="9"/>
       <c r="J357" s="9"/>
       <c r="L357" s="12"/>
-      <c r="N357" s="19"/>
+      <c r="N357" s="20"/>
     </row>
     <row r="358" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A358" s="9"/>
       <c r="J358" s="9"/>
       <c r="L358" s="12"/>
-      <c r="N358" s="19"/>
+      <c r="N358" s="20"/>
     </row>
     <row r="359" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A359" s="9"/>
       <c r="J359" s="9"/>
       <c r="L359" s="12"/>
-      <c r="N359" s="19"/>
+      <c r="N359" s="20"/>
     </row>
     <row r="360" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A360" s="9"/>
       <c r="J360" s="9"/>
       <c r="L360" s="12"/>
-      <c r="N360" s="19"/>
+      <c r="N360" s="20"/>
     </row>
     <row r="361" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A361" s="9"/>
       <c r="J361" s="9"/>
       <c r="L361" s="12"/>
-      <c r="N361" s="19"/>
+      <c r="N361" s="20"/>
     </row>
     <row r="362" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A362" s="9"/>
       <c r="J362" s="9"/>
       <c r="L362" s="12"/>
-      <c r="N362" s="19"/>
+      <c r="N362" s="20"/>
     </row>
     <row r="363" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A363" s="9"/>
       <c r="J363" s="9"/>
       <c r="L363" s="12"/>
-      <c r="N363" s="19"/>
+      <c r="N363" s="20"/>
     </row>
     <row r="364" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A364" s="9"/>
       <c r="J364" s="9"/>
       <c r="L364" s="12"/>
-      <c r="N364" s="19"/>
+      <c r="N364" s="20"/>
     </row>
     <row r="365" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A365" s="9"/>
       <c r="J365" s="9"/>
       <c r="L365" s="12"/>
-      <c r="N365" s="19"/>
+      <c r="N365" s="20"/>
     </row>
     <row r="366" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A366" s="9"/>
       <c r="J366" s="9"/>
       <c r="L366" s="12"/>
-      <c r="N366" s="19"/>
+      <c r="N366" s="20"/>
     </row>
     <row r="367" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A367" s="9"/>
       <c r="J367" s="9"/>
       <c r="L367" s="12"/>
-      <c r="N367" s="19"/>
+      <c r="N367" s="20"/>
     </row>
     <row r="368" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A368" s="9"/>
       <c r="J368" s="9"/>
       <c r="L368" s="12"/>
-      <c r="N368" s="19"/>
+      <c r="N368" s="20"/>
     </row>
     <row r="369" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A369" s="9"/>
       <c r="J369" s="9"/>
       <c r="L369" s="12"/>
-      <c r="N369" s="19"/>
+      <c r="N369" s="20"/>
     </row>
     <row r="370" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A370" s="9"/>
       <c r="J370" s="9"/>
       <c r="L370" s="12"/>
-      <c r="N370" s="19"/>
+      <c r="N370" s="20"/>
     </row>
     <row r="371" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A371" s="9"/>
       <c r="J371" s="9"/>
       <c r="L371" s="12"/>
-      <c r="N371" s="19"/>
+      <c r="N371" s="20"/>
     </row>
     <row r="372" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A372" s="9"/>
       <c r="J372" s="9"/>
       <c r="L372" s="12"/>
-      <c r="N372" s="19"/>
+      <c r="N372" s="20"/>
     </row>
     <row r="373" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A373" s="9"/>
       <c r="J373" s="9"/>
       <c r="L373" s="12"/>
-      <c r="N373" s="19"/>
+      <c r="N373" s="20"/>
     </row>
     <row r="374" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A374" s="9"/>
       <c r="J374" s="9"/>
       <c r="L374" s="12"/>
-      <c r="N374" s="19"/>
+      <c r="N374" s="20"/>
     </row>
     <row r="375" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A375" s="9"/>
       <c r="J375" s="9"/>
       <c r="L375" s="12"/>
-      <c r="N375" s="19"/>
+      <c r="N375" s="20"/>
     </row>
     <row r="376" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A376" s="9"/>
       <c r="J376" s="9"/>
       <c r="L376" s="12"/>
-      <c r="N376" s="19"/>
+      <c r="N376" s="20"/>
     </row>
     <row r="377" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A377" s="9"/>
       <c r="J377" s="9"/>
       <c r="L377" s="12"/>
-      <c r="N377" s="19"/>
+      <c r="N377" s="20"/>
     </row>
     <row r="378" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A378" s="9"/>
       <c r="J378" s="9"/>
       <c r="L378" s="12"/>
-      <c r="N378" s="19"/>
+      <c r="N378" s="20"/>
     </row>
     <row r="379" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A379" s="9"/>
       <c r="J379" s="9"/>
       <c r="L379" s="12"/>
-      <c r="N379" s="19"/>
+      <c r="N379" s="20"/>
     </row>
     <row r="380" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A380" s="9"/>
       <c r="J380" s="9"/>
       <c r="L380" s="12"/>
-      <c r="N380" s="19"/>
+      <c r="N380" s="20"/>
     </row>
     <row r="381" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A381" s="9"/>
       <c r="J381" s="9"/>
       <c r="L381" s="12"/>
-      <c r="N381" s="19"/>
+      <c r="N381" s="20"/>
     </row>
     <row r="382" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A382" s="9"/>
       <c r="J382" s="9"/>
       <c r="L382" s="12"/>
-      <c r="N382" s="19"/>
+      <c r="N382" s="20"/>
     </row>
     <row r="383" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A383" s="9"/>
       <c r="J383" s="9"/>
       <c r="L383" s="12"/>
-      <c r="N383" s="19"/>
+      <c r="N383" s="20"/>
     </row>
     <row r="384" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A384" s="9"/>
       <c r="J384" s="9"/>
       <c r="L384" s="12"/>
-      <c r="N384" s="19"/>
+      <c r="N384" s="20"/>
     </row>
     <row r="385" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A385" s="9"/>
       <c r="J385" s="9"/>
       <c r="L385" s="12"/>
-      <c r="N385" s="19"/>
+      <c r="N385" s="20"/>
     </row>
     <row r="386" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A386" s="9"/>
       <c r="J386" s="9"/>
       <c r="L386" s="12"/>
-      <c r="N386" s="19"/>
+      <c r="N386" s="20"/>
     </row>
     <row r="387" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A387" s="9"/>
       <c r="J387" s="9"/>
       <c r="L387" s="12"/>
-      <c r="N387" s="19"/>
+      <c r="N387" s="20"/>
     </row>
     <row r="388" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A388" s="9"/>
       <c r="J388" s="9"/>
       <c r="L388" s="12"/>
-      <c r="N388" s="19"/>
+      <c r="N388" s="20"/>
     </row>
     <row r="389" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A389" s="9"/>
       <c r="J389" s="9"/>
       <c r="L389" s="12"/>
-      <c r="N389" s="19"/>
+      <c r="N389" s="20"/>
     </row>
     <row r="390" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A390" s="9"/>
       <c r="J390" s="9"/>
       <c r="L390" s="12"/>
-      <c r="N390" s="19"/>
+      <c r="N390" s="20"/>
     </row>
     <row r="391" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A391" s="9"/>
       <c r="J391" s="9"/>
       <c r="L391" s="12"/>
-      <c r="N391" s="19"/>
+      <c r="N391" s="20"/>
     </row>
     <row r="392" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A392" s="9"/>
       <c r="J392" s="9"/>
       <c r="L392" s="12"/>
-      <c r="N392" s="19"/>
+      <c r="N392" s="20"/>
     </row>
     <row r="393" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A393" s="9"/>
       <c r="J393" s="9"/>
       <c r="L393" s="12"/>
-      <c r="N393" s="19"/>
+      <c r="N393" s="20"/>
     </row>
     <row r="394" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A394" s="9"/>
       <c r="J394" s="9"/>
       <c r="L394" s="12"/>
-      <c r="N394" s="19"/>
+      <c r="N394" s="20"/>
     </row>
     <row r="395" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A395" s="9"/>
       <c r="J395" s="9"/>
       <c r="L395" s="12"/>
-      <c r="N395" s="19"/>
+      <c r="N395" s="20"/>
     </row>
     <row r="396" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A396" s="9"/>
       <c r="J396" s="9"/>
       <c r="L396" s="12"/>
-      <c r="N396" s="19"/>
+      <c r="N396" s="20"/>
     </row>
     <row r="397" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A397" s="9"/>
       <c r="J397" s="9"/>
       <c r="L397" s="12"/>
-      <c r="N397" s="19"/>
+      <c r="N397" s="20"/>
     </row>
     <row r="398" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A398" s="9"/>
       <c r="J398" s="9"/>
       <c r="L398" s="12"/>
-      <c r="N398" s="19"/>
+      <c r="N398" s="20"/>
     </row>
     <row r="399" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A399" s="9"/>
       <c r="J399" s="9"/>
       <c r="L399" s="12"/>
-      <c r="N399" s="19"/>
+      <c r="N399" s="20"/>
     </row>
     <row r="400" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A400" s="9"/>
       <c r="J400" s="9"/>
       <c r="L400" s="12"/>
-      <c r="N400" s="19"/>
+      <c r="N400" s="20"/>
     </row>
     <row r="401" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A401" s="9"/>
       <c r="J401" s="9"/>
       <c r="L401" s="12"/>
-      <c r="N401" s="19"/>
+      <c r="N401" s="20"/>
     </row>
     <row r="402" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A402" s="9"/>
       <c r="J402" s="9"/>
       <c r="L402" s="12"/>
-      <c r="N402" s="19"/>
+      <c r="N402" s="20"/>
     </row>
     <row r="403" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A403" s="9"/>
       <c r="J403" s="9"/>
       <c r="L403" s="12"/>
-      <c r="N403" s="19"/>
+      <c r="N403" s="20"/>
     </row>
     <row r="404" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A404" s="9"/>
       <c r="J404" s="9"/>
       <c r="L404" s="12"/>
-      <c r="N404" s="19"/>
+      <c r="N404" s="20"/>
     </row>
     <row r="405" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A405" s="9"/>
       <c r="J405" s="9"/>
       <c r="L405" s="12"/>
-      <c r="N405" s="19"/>
+      <c r="N405" s="20"/>
     </row>
     <row r="406" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A406" s="9"/>
       <c r="J406" s="9"/>
       <c r="L406" s="12"/>
-      <c r="N406" s="19"/>
+      <c r="N406" s="20"/>
     </row>
     <row r="407" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A407" s="9"/>
       <c r="J407" s="9"/>
       <c r="L407" s="12"/>
-      <c r="N407" s="19"/>
+      <c r="N407" s="20"/>
     </row>
     <row r="408" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A408" s="9"/>
       <c r="J408" s="9"/>
       <c r="L408" s="12"/>
-      <c r="N408" s="19"/>
+      <c r="N408" s="20"/>
     </row>
     <row r="409" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A409" s="9"/>
       <c r="J409" s="9"/>
       <c r="L409" s="12"/>
-      <c r="N409" s="19"/>
+      <c r="N409" s="20"/>
     </row>
     <row r="410" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A410" s="9"/>
       <c r="J410" s="9"/>
       <c r="L410" s="12"/>
-      <c r="N410" s="19"/>
+      <c r="N410" s="20"/>
     </row>
     <row r="411" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A411" s="9"/>
       <c r="J411" s="9"/>
       <c r="L411" s="12"/>
-      <c r="N411" s="19"/>
+      <c r="N411" s="20"/>
     </row>
     <row r="412" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A412" s="9"/>
       <c r="J412" s="9"/>
       <c r="L412" s="12"/>
-      <c r="N412" s="19"/>
+      <c r="N412" s="20"/>
     </row>
     <row r="413" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A413" s="9"/>
       <c r="J413" s="9"/>
       <c r="L413" s="12"/>
-      <c r="N413" s="19"/>
+      <c r="N413" s="20"/>
     </row>
     <row r="414" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A414" s="9"/>
       <c r="J414" s="9"/>
       <c r="L414" s="12"/>
-      <c r="N414" s="19"/>
+      <c r="N414" s="20"/>
     </row>
     <row r="415" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A415" s="9"/>
       <c r="J415" s="9"/>
       <c r="L415" s="12"/>
-      <c r="N415" s="19"/>
+      <c r="N415" s="20"/>
     </row>
     <row r="416" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A416" s="9"/>
       <c r="J416" s="9"/>
       <c r="L416" s="12"/>
-      <c r="N416" s="19"/>
+      <c r="N416" s="20"/>
     </row>
     <row r="417" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A417" s="9"/>
       <c r="J417" s="9"/>
       <c r="L417" s="12"/>
-      <c r="N417" s="19"/>
+      <c r="N417" s="20"/>
     </row>
     <row r="418" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A418" s="9"/>
       <c r="J418" s="9"/>
       <c r="L418" s="12"/>
-      <c r="N418" s="19"/>
+      <c r="N418" s="20"/>
     </row>
     <row r="419" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A419" s="9"/>
       <c r="J419" s="9"/>
       <c r="L419" s="12"/>
-      <c r="N419" s="19"/>
+      <c r="N419" s="20"/>
     </row>
     <row r="420" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A420" s="9"/>
       <c r="J420" s="9"/>
       <c r="L420" s="12"/>
-      <c r="N420" s="19"/>
+      <c r="N420" s="20"/>
     </row>
     <row r="421" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A421" s="9"/>
       <c r="J421" s="9"/>
       <c r="L421" s="12"/>
-      <c r="N421" s="19"/>
+      <c r="N421" s="20"/>
     </row>
     <row r="422" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A422" s="9"/>
       <c r="J422" s="9"/>
       <c r="L422" s="12"/>
-      <c r="N422" s="19"/>
+      <c r="N422" s="20"/>
     </row>
     <row r="423" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A423" s="9"/>
       <c r="J423" s="9"/>
       <c r="L423" s="12"/>
-      <c r="N423" s="19"/>
+      <c r="N423" s="20"/>
     </row>
     <row r="424" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A424" s="9"/>
       <c r="J424" s="9"/>
       <c r="L424" s="12"/>
-      <c r="N424" s="19"/>
+      <c r="N424" s="20"/>
     </row>
     <row r="425" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A425" s="9"/>
       <c r="J425" s="9"/>
       <c r="L425" s="12"/>
-      <c r="N425" s="19"/>
+      <c r="N425" s="20"/>
     </row>
     <row r="426" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A426" s="9"/>
       <c r="J426" s="9"/>
       <c r="L426" s="12"/>
-      <c r="N426" s="19"/>
+      <c r="N426" s="20"/>
     </row>
     <row r="427" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A427" s="9"/>
       <c r="J427" s="9"/>
       <c r="L427" s="12"/>
-      <c r="N427" s="19"/>
+      <c r="N427" s="20"/>
     </row>
     <row r="428" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A428" s="9"/>
       <c r="J428" s="9"/>
       <c r="L428" s="12"/>
-      <c r="N428" s="19"/>
+      <c r="N428" s="20"/>
     </row>
     <row r="429" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A429" s="9"/>
       <c r="J429" s="9"/>
       <c r="L429" s="12"/>
-      <c r="N429" s="19"/>
+      <c r="N429" s="20"/>
     </row>
     <row r="430" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A430" s="9"/>
       <c r="J430" s="9"/>
       <c r="L430" s="12"/>
-      <c r="N430" s="19"/>
+      <c r="N430" s="20"/>
     </row>
     <row r="431" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A431" s="9"/>
       <c r="J431" s="9"/>
       <c r="L431" s="12"/>
-      <c r="N431" s="19"/>
+      <c r="N431" s="20"/>
     </row>
     <row r="432" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A432" s="9"/>
       <c r="J432" s="9"/>
       <c r="L432" s="12"/>
-      <c r="N432" s="19"/>
+      <c r="N432" s="20"/>
     </row>
     <row r="433" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A433" s="9"/>
       <c r="J433" s="9"/>
       <c r="L433" s="12"/>
-      <c r="N433" s="19"/>
+      <c r="N433" s="20"/>
     </row>
     <row r="434" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A434" s="9"/>
       <c r="J434" s="9"/>
       <c r="L434" s="12"/>
-      <c r="N434" s="19"/>
+      <c r="N434" s="20"/>
     </row>
     <row r="435" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A435" s="9"/>
       <c r="J435" s="9"/>
       <c r="L435" s="12"/>
-      <c r="N435" s="19"/>
+      <c r="N435" s="20"/>
     </row>
     <row r="436" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A436" s="9"/>
       <c r="J436" s="9"/>
       <c r="L436" s="12"/>
-      <c r="N436" s="19"/>
+      <c r="N436" s="20"/>
     </row>
     <row r="437" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A437" s="9"/>
       <c r="J437" s="9"/>
       <c r="L437" s="12"/>
-      <c r="N437" s="19"/>
+      <c r="N437" s="20"/>
     </row>
     <row r="438" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A438" s="9"/>
       <c r="J438" s="9"/>
       <c r="L438" s="12"/>
-      <c r="N438" s="19"/>
+      <c r="N438" s="20"/>
     </row>
     <row r="439" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A439" s="9"/>
       <c r="J439" s="9"/>
       <c r="L439" s="12"/>
-      <c r="N439" s="19"/>
+      <c r="N439" s="20"/>
     </row>
     <row r="440" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A440" s="9"/>
       <c r="J440" s="9"/>
       <c r="L440" s="12"/>
-      <c r="N440" s="19"/>
+      <c r="N440" s="20"/>
     </row>
     <row r="441" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A441" s="9"/>
       <c r="J441" s="9"/>
       <c r="L441" s="12"/>
-      <c r="N441" s="19"/>
+      <c r="N441" s="20"/>
     </row>
     <row r="442" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A442" s="9"/>
       <c r="J442" s="9"/>
       <c r="L442" s="12"/>
-      <c r="N442" s="19"/>
+      <c r="N442" s="20"/>
     </row>
     <row r="443" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A443" s="9"/>
       <c r="J443" s="9"/>
       <c r="L443" s="12"/>
-      <c r="N443" s="19"/>
+      <c r="N443" s="20"/>
     </row>
     <row r="444" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A444" s="9"/>
       <c r="J444" s="9"/>
       <c r="L444" s="12"/>
-      <c r="N444" s="19"/>
+      <c r="N444" s="20"/>
     </row>
     <row r="445" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A445" s="9"/>
       <c r="J445" s="9"/>
       <c r="L445" s="12"/>
-      <c r="N445" s="19"/>
+      <c r="N445" s="20"/>
     </row>
     <row r="446" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A446" s="9"/>
       <c r="J446" s="9"/>
       <c r="L446" s="12"/>
-      <c r="N446" s="19"/>
+      <c r="N446" s="20"/>
     </row>
     <row r="447" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A447" s="9"/>
       <c r="J447" s="9"/>
       <c r="L447" s="12"/>
-      <c r="N447" s="19"/>
+      <c r="N447" s="20"/>
     </row>
     <row r="448" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A448" s="9"/>
       <c r="J448" s="9"/>
       <c r="L448" s="12"/>
-      <c r="N448" s="19"/>
+      <c r="N448" s="20"/>
     </row>
     <row r="449" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A449" s="9"/>
       <c r="J449" s="9"/>
       <c r="L449" s="12"/>
-      <c r="N449" s="19"/>
+      <c r="N449" s="20"/>
     </row>
     <row r="450" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A450" s="9"/>
       <c r="J450" s="9"/>
       <c r="L450" s="12"/>
-      <c r="N450" s="19"/>
+      <c r="N450" s="20"/>
     </row>
     <row r="451" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A451" s="9"/>
       <c r="J451" s="9"/>
       <c r="L451" s="12"/>
-      <c r="N451" s="19"/>
+      <c r="N451" s="20"/>
     </row>
     <row r="452" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A452" s="9"/>
       <c r="J452" s="9"/>
       <c r="L452" s="12"/>
-      <c r="N452" s="19"/>
+      <c r="N452" s="20"/>
     </row>
     <row r="453" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A453" s="9"/>
       <c r="J453" s="9"/>
       <c r="L453" s="12"/>
-      <c r="N453" s="19"/>
+      <c r="N453" s="20"/>
     </row>
     <row r="454" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A454" s="9"/>
       <c r="J454" s="9"/>
       <c r="L454" s="12"/>
-      <c r="N454" s="19"/>
+      <c r="N454" s="20"/>
     </row>
     <row r="455" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A455" s="9"/>
       <c r="J455" s="9"/>
       <c r="L455" s="12"/>
-      <c r="N455" s="19"/>
+      <c r="N455" s="20"/>
     </row>
     <row r="456" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A456" s="9"/>
       <c r="J456" s="9"/>
       <c r="L456" s="12"/>
-      <c r="N456" s="19"/>
+      <c r="N456" s="20"/>
     </row>
     <row r="457" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A457" s="9"/>
       <c r="J457" s="9"/>
       <c r="L457" s="12"/>
-      <c r="N457" s="19"/>
+      <c r="N457" s="20"/>
     </row>
     <row r="458" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A458" s="9"/>
       <c r="J458" s="9"/>
       <c r="L458" s="12"/>
-      <c r="N458" s="19"/>
+      <c r="N458" s="20"/>
     </row>
     <row r="459" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A459" s="9"/>
       <c r="J459" s="9"/>
       <c r="L459" s="12"/>
-      <c r="N459" s="19"/>
+      <c r="N459" s="20"/>
     </row>
     <row r="460" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A460" s="9"/>
       <c r="J460" s="9"/>
       <c r="L460" s="12"/>
-      <c r="N460" s="19"/>
+      <c r="N460" s="20"/>
     </row>
     <row r="461" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A461" s="9"/>
       <c r="J461" s="9"/>
       <c r="L461" s="12"/>
-      <c r="N461" s="19"/>
+      <c r="N461" s="20"/>
     </row>
     <row r="462" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A462" s="9"/>
       <c r="J462" s="9"/>
       <c r="L462" s="12"/>
-      <c r="N462" s="19"/>
+      <c r="N462" s="20"/>
     </row>
     <row r="463" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A463" s="9"/>
       <c r="J463" s="9"/>
       <c r="L463" s="12"/>
-      <c r="N463" s="19"/>
+      <c r="N463" s="20"/>
     </row>
     <row r="464" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A464" s="9"/>
       <c r="J464" s="9"/>
       <c r="L464" s="12"/>
-      <c r="N464" s="19"/>
+      <c r="N464" s="20"/>
     </row>
     <row r="465" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A465" s="9"/>
       <c r="J465" s="9"/>
       <c r="L465" s="12"/>
-      <c r="N465" s="19"/>
+      <c r="N465" s="20"/>
     </row>
     <row r="466" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A466" s="9"/>
       <c r="J466" s="9"/>
       <c r="L466" s="12"/>
-      <c r="N466" s="19"/>
+      <c r="N466" s="20"/>
     </row>
     <row r="467" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A467" s="9"/>
       <c r="J467" s="9"/>
       <c r="L467" s="12"/>
-      <c r="N467" s="19"/>
+      <c r="N467" s="20"/>
     </row>
     <row r="468" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A468" s="9"/>
       <c r="J468" s="9"/>
       <c r="L468" s="12"/>
-      <c r="N468" s="19"/>
+      <c r="N468" s="20"/>
     </row>
     <row r="469" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A469" s="9"/>
       <c r="J469" s="9"/>
       <c r="L469" s="12"/>
-      <c r="N469" s="19"/>
+      <c r="N469" s="20"/>
     </row>
     <row r="470" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A470" s="9"/>
       <c r="J470" s="9"/>
       <c r="L470" s="12"/>
-      <c r="N470" s="19"/>
+      <c r="N470" s="20"/>
     </row>
     <row r="471" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A471" s="9"/>
       <c r="J471" s="9"/>
       <c r="L471" s="12"/>
-      <c r="N471" s="19"/>
+      <c r="N471" s="20"/>
     </row>
     <row r="472" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A472" s="9"/>
       <c r="J472" s="9"/>
       <c r="L472" s="12"/>
-      <c r="N472" s="19"/>
+      <c r="N472" s="20"/>
     </row>
     <row r="473" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A473" s="9"/>
       <c r="J473" s="9"/>
       <c r="L473" s="12"/>
-      <c r="N473" s="19"/>
+      <c r="N473" s="20"/>
     </row>
     <row r="474" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A474" s="9"/>
       <c r="J474" s="9"/>
       <c r="L474" s="12"/>
-      <c r="N474" s="19"/>
+      <c r="N474" s="20"/>
     </row>
     <row r="475" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A475" s="9"/>
       <c r="J475" s="9"/>
       <c r="L475" s="12"/>
-      <c r="N475" s="19"/>
+      <c r="N475" s="20"/>
     </row>
     <row r="476" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A476" s="9"/>
       <c r="J476" s="9"/>
       <c r="L476" s="12"/>
-      <c r="N476" s="19"/>
+      <c r="N476" s="20"/>
     </row>
     <row r="477" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A477" s="9"/>
       <c r="J477" s="9"/>
       <c r="L477" s="12"/>
-      <c r="N477" s="19"/>
+      <c r="N477" s="20"/>
     </row>
     <row r="478" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A478" s="9"/>
       <c r="J478" s="9"/>
       <c r="L478" s="12"/>
-      <c r="N478" s="19"/>
+      <c r="N478" s="20"/>
     </row>
     <row r="479" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A479" s="9"/>
       <c r="J479" s="9"/>
       <c r="L479" s="12"/>
-      <c r="N479" s="19"/>
+      <c r="N479" s="20"/>
     </row>
     <row r="480" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A480" s="9"/>
       <c r="J480" s="9"/>
       <c r="L480" s="12"/>
-      <c r="N480" s="19"/>
+      <c r="N480" s="20"/>
     </row>
     <row r="481" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A481" s="9"/>
       <c r="J481" s="9"/>
       <c r="L481" s="12"/>
-      <c r="N481" s="19"/>
+      <c r="N481" s="20"/>
     </row>
     <row r="482" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A482" s="9"/>
       <c r="J482" s="9"/>
       <c r="L482" s="12"/>
-      <c r="N482" s="19"/>
+      <c r="N482" s="20"/>
     </row>
     <row r="483" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A483" s="9"/>
       <c r="J483" s="9"/>
       <c r="L483" s="12"/>
-      <c r="N483" s="19"/>
+      <c r="N483" s="20"/>
     </row>
     <row r="484" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A484" s="9"/>
       <c r="J484" s="9"/>
       <c r="L484" s="12"/>
-      <c r="N484" s="19"/>
+      <c r="N484" s="20"/>
     </row>
     <row r="485" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A485" s="9"/>
       <c r="J485" s="9"/>
       <c r="L485" s="12"/>
-      <c r="N485" s="19"/>
+      <c r="N485" s="20"/>
     </row>
     <row r="486" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A486" s="9"/>
       <c r="J486" s="9"/>
       <c r="L486" s="12"/>
-      <c r="N486" s="19"/>
+      <c r="N486" s="20"/>
     </row>
     <row r="487" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A487" s="9"/>
       <c r="J487" s="9"/>
       <c r="L487" s="12"/>
-      <c r="N487" s="19"/>
+      <c r="N487" s="20"/>
     </row>
     <row r="488" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A488" s="9"/>
       <c r="J488" s="9"/>
       <c r="L488" s="12"/>
-      <c r="N488" s="19"/>
+      <c r="N488" s="20"/>
     </row>
     <row r="489" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A489" s="9"/>
       <c r="J489" s="9"/>
       <c r="L489" s="12"/>
-      <c r="N489" s="19"/>
+      <c r="N489" s="20"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AF489"/>
